--- a/output_watermarked.xlsx
+++ b/output_watermarked.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookPr codeName="ThisWorkbook"/>
+  <x:workbookProtection workbookPassword="8CAE" lockStructure="1"/>
   <x:bookViews>
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
@@ -20,6 +21,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>Health Insurance Claims Experience Form</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
   </x:si>
   <x:si>
@@ -1788,9 +1792,6 @@
   </x:si>
   <x:si>
     <x:t>Page 5 of 5</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
 </x:sst>
 </file>
@@ -2454,7 +2455,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:34" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -2492,7 +2493,7 @@
     </x:row>
     <x:row r="2" spans="1:34" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -2531,13 +2532,13 @@
     <x:row r="3" spans="1:34">
       <x:c r="A3" s="4"/>
       <x:c r="B3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="4"/>
       <x:c r="H3" s="4"/>
@@ -2555,7 +2556,7 @@
       <x:c r="T3" s="4"/>
       <x:c r="U3" s="4"/>
       <x:c r="V3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W3" s="4"/>
       <x:c r="X3" s="4"/>
@@ -2564,7 +2565,7 @@
       <x:c r="AA3" s="4"/>
       <x:c r="AB3" s="4"/>
       <x:c r="AC3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD3" s="4"/>
       <x:c r="AE3" s="4"/>
@@ -2575,7 +2576,7 @@
     <x:row r="4" spans="1:34">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -2587,7 +2588,7 @@
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M4" s="4"/>
       <x:c r="N4" s="4"/>
@@ -2599,7 +2600,7 @@
       <x:c r="T4" s="4"/>
       <x:c r="U4" s="4"/>
       <x:c r="V4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="W4" s="4"/>
       <x:c r="X4" s="4"/>
@@ -2609,7 +2610,7 @@
       <x:c r="AB4" s="4"/>
       <x:c r="AC4" s="4"/>
       <x:c r="AD4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AE4" s="4"/>
       <x:c r="AF4" s="4"/>
@@ -2619,7 +2620,7 @@
     <x:row r="5" spans="1:34">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -2631,7 +2632,7 @@
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M5" s="4"/>
       <x:c r="N5" s="4"/>
@@ -2643,7 +2644,7 @@
       <x:c r="T5" s="4"/>
       <x:c r="U5" s="4"/>
       <x:c r="V5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="W5" s="4"/>
       <x:c r="X5" s="4"/>
@@ -2652,7 +2653,7 @@
       <x:c r="AA5" s="4"/>
       <x:c r="AB5" s="4"/>
       <x:c r="AC5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AD5" s="4"/>
       <x:c r="AE5" s="4"/>
@@ -2663,7 +2664,7 @@
     <x:row r="6" spans="1:34">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -2675,7 +2676,7 @@
       <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M6" s="4"/>
       <x:c r="N6" s="4"/>
@@ -2687,7 +2688,7 @@
       <x:c r="T6" s="4"/>
       <x:c r="U6" s="4"/>
       <x:c r="V6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="W6" s="4"/>
       <x:c r="X6" s="4"/>
@@ -2698,7 +2699,7 @@
       <x:c r="AC6" s="4"/>
       <x:c r="AD6" s="4"/>
       <x:c r="AE6" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AF6" s="4"/>
       <x:c r="AG6" s="4"/>
@@ -2707,7 +2708,7 @@
     <x:row r="7" spans="1:34">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -2716,7 +2717,7 @@
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
@@ -2731,7 +2732,7 @@
       <x:c r="T7" s="4"/>
       <x:c r="U7" s="4"/>
       <x:c r="V7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="W7" s="4"/>
       <x:c r="X7" s="4"/>
@@ -2742,7 +2743,7 @@
       <x:c r="AC7" s="4"/>
       <x:c r="AD7" s="4"/>
       <x:c r="AE7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AF7" s="4"/>
       <x:c r="AG7" s="4"/>
@@ -2751,12 +2752,12 @@
     <x:row r="8" spans="1:34">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
@@ -2783,7 +2784,7 @@
       <x:c r="AB8" s="4"/>
       <x:c r="AC8" s="4"/>
       <x:c r="AD8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AE8" s="4"/>
       <x:c r="AF8" s="4"/>
@@ -2798,43 +2799,43 @@
       <x:c r="E9" s="4"/>
       <x:c r="F9" s="4"/>
       <x:c r="G9" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L9" s="4"/>
       <x:c r="M9" s="4"/>
       <x:c r="N9" s="4"/>
       <x:c r="O9" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P9" s="4"/>
       <x:c r="Q9" s="4"/>
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T9" s="4"/>
       <x:c r="U9" s="4"/>
       <x:c r="V9" s="4"/>
       <x:c r="W9" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="X9" s="4"/>
       <x:c r="Y9" s="4"/>
       <x:c r="Z9" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AA9" s="4"/>
       <x:c r="AB9" s="4"/>
       <x:c r="AC9" s="4"/>
       <x:c r="AD9" s="4"/>
       <x:c r="AE9" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AF9" s="4"/>
       <x:c r="AG9" s="4"/>
@@ -2844,13 +2845,13 @@
       <x:c r="A10" s="4"/>
       <x:c r="B10" s="4"/>
       <x:c r="C10" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="4"/>
       <x:c r="E10" s="4"/>
       <x:c r="F10" s="4"/>
       <x:c r="G10" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
@@ -2858,34 +2859,34 @@
       <x:c r="K10" s="4"/>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="T10" s="4"/>
       <x:c r="U10" s="4"/>
       <x:c r="V10" s="4"/>
       <x:c r="W10" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="X10" s="4"/>
       <x:c r="Y10" s="4"/>
       <x:c r="Z10" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AA10" s="4"/>
       <x:c r="AB10" s="4"/>
       <x:c r="AC10" s="4"/>
       <x:c r="AD10" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AE10" s="4"/>
       <x:c r="AF10" s="4"/>
@@ -2914,7 +2915,7 @@
       <x:c r="S11" s="4"/>
       <x:c r="T11" s="4"/>
       <x:c r="U11" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="V11" s="4"/>
       <x:c r="W11" s="4"/>
@@ -2922,7 +2923,7 @@
       <x:c r="Y11" s="4"/>
       <x:c r="Z11" s="4"/>
       <x:c r="AA11" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AB11" s="4"/>
       <x:c r="AC11" s="4"/>
@@ -2931,13 +2932,13 @@
       <x:c r="AF11" s="4"/>
       <x:c r="AG11" s="4"/>
       <x:c r="AH11" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:34">
       <x:c r="A12" s="4"/>
       <x:c r="B12" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="4"/>
       <x:c r="D12" s="4"/>
@@ -2976,7 +2977,7 @@
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
@@ -3013,7 +3014,7 @@
     <x:row r="14" spans="1:34">
       <x:c r="A14" s="4"/>
       <x:c r="B14" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="4"/>
@@ -3021,7 +3022,7 @@
       <x:c r="F14" s="4"/>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -3055,43 +3056,43 @@
       <x:c r="B15" s="4"/>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E15" s="4"/>
       <x:c r="F15" s="4"/>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
       <x:c r="K15" s="4"/>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N15" s="4"/>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4"/>
       <x:c r="T15" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U15" s="4"/>
       <x:c r="V15" s="4"/>
       <x:c r="W15" s="4"/>
       <x:c r="X15" s="4"/>
       <x:c r="Y15" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z15" s="4"/>
       <x:c r="AA15" s="4"/>
       <x:c r="AB15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC15" s="4"/>
       <x:c r="AD15" s="4"/>
@@ -3099,7 +3100,7 @@
       <x:c r="AF15" s="4"/>
       <x:c r="AG15" s="4"/>
       <x:c r="AH15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:34">
@@ -3107,43 +3108,43 @@
       <x:c r="B16" s="4"/>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="5" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E16" s="4"/>
       <x:c r="F16" s="4"/>
       <x:c r="G16" s="4"/>
       <x:c r="H16" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I16" s="4"/>
       <x:c r="J16" s="4"/>
       <x:c r="K16" s="4"/>
       <x:c r="L16" s="4"/>
       <x:c r="M16" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
       <x:c r="Q16" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4"/>
       <x:c r="T16" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="U16" s="4"/>
       <x:c r="V16" s="4"/>
       <x:c r="W16" s="4"/>
       <x:c r="X16" s="4"/>
       <x:c r="Y16" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z16" s="4"/>
       <x:c r="AA16" s="4"/>
       <x:c r="AB16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC16" s="4"/>
       <x:c r="AD16" s="4"/>
@@ -3151,7 +3152,7 @@
       <x:c r="AF16" s="4"/>
       <x:c r="AG16" s="4"/>
       <x:c r="AH16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:34">
@@ -3159,43 +3160,43 @@
       <x:c r="B17" s="4"/>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="5" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E17" s="4"/>
       <x:c r="F17" s="4"/>
       <x:c r="G17" s="4"/>
       <x:c r="H17" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I17" s="4"/>
       <x:c r="J17" s="4"/>
       <x:c r="K17" s="4"/>
       <x:c r="L17" s="4"/>
       <x:c r="M17" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N17" s="4"/>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
       <x:c r="Q17" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="R17" s="4"/>
       <x:c r="S17" s="4"/>
       <x:c r="T17" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="U17" s="4"/>
       <x:c r="V17" s="4"/>
       <x:c r="W17" s="4"/>
       <x:c r="X17" s="4"/>
       <x:c r="Y17" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z17" s="4"/>
       <x:c r="AA17" s="4"/>
       <x:c r="AB17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC17" s="4"/>
       <x:c r="AD17" s="4"/>
@@ -3203,7 +3204,7 @@
       <x:c r="AF17" s="4"/>
       <x:c r="AG17" s="4"/>
       <x:c r="AH17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:34">
@@ -3211,43 +3212,43 @@
       <x:c r="B18" s="4"/>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E18" s="4"/>
       <x:c r="F18" s="4"/>
       <x:c r="G18" s="4"/>
       <x:c r="H18" s="6" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I18" s="4"/>
       <x:c r="J18" s="4"/>
       <x:c r="K18" s="4"/>
       <x:c r="L18" s="4"/>
       <x:c r="M18" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N18" s="4"/>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="4"/>
       <x:c r="Q18" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R18" s="4"/>
       <x:c r="S18" s="4"/>
       <x:c r="T18" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="U18" s="4"/>
       <x:c r="V18" s="4"/>
       <x:c r="W18" s="4"/>
       <x:c r="X18" s="4"/>
       <x:c r="Y18" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z18" s="4"/>
       <x:c r="AA18" s="4"/>
       <x:c r="AB18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC18" s="4"/>
       <x:c r="AD18" s="4"/>
@@ -3255,7 +3256,7 @@
       <x:c r="AF18" s="4"/>
       <x:c r="AG18" s="4"/>
       <x:c r="AH18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:34">
@@ -3263,43 +3264,43 @@
       <x:c r="B19" s="4"/>
       <x:c r="C19" s="4"/>
       <x:c r="D19" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E19" s="4"/>
       <x:c r="F19" s="4"/>
       <x:c r="G19" s="4"/>
       <x:c r="H19" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I19" s="4"/>
       <x:c r="J19" s="4"/>
       <x:c r="K19" s="4"/>
       <x:c r="L19" s="4"/>
       <x:c r="M19" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N19" s="4"/>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="4"/>
       <x:c r="Q19" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="R19" s="4"/>
       <x:c r="S19" s="4"/>
       <x:c r="T19" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="U19" s="4"/>
       <x:c r="V19" s="4"/>
       <x:c r="W19" s="4"/>
       <x:c r="X19" s="4"/>
       <x:c r="Y19" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z19" s="4"/>
       <x:c r="AA19" s="4"/>
       <x:c r="AB19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC19" s="4"/>
       <x:c r="AD19" s="4"/>
@@ -3307,7 +3308,7 @@
       <x:c r="AF19" s="4"/>
       <x:c r="AG19" s="4"/>
       <x:c r="AH19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:34">
@@ -3315,43 +3316,43 @@
       <x:c r="B20" s="4"/>
       <x:c r="C20" s="4"/>
       <x:c r="D20" s="5" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E20" s="4"/>
       <x:c r="F20" s="4"/>
       <x:c r="G20" s="4"/>
       <x:c r="H20" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I20" s="4"/>
       <x:c r="J20" s="4"/>
       <x:c r="K20" s="4"/>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="N20" s="4"/>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="4"/>
       <x:c r="Q20" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="R20" s="4"/>
       <x:c r="S20" s="4"/>
       <x:c r="T20" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="U20" s="4"/>
       <x:c r="V20" s="4"/>
       <x:c r="W20" s="4"/>
       <x:c r="X20" s="4"/>
       <x:c r="Y20" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z20" s="4"/>
       <x:c r="AA20" s="4"/>
       <x:c r="AB20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC20" s="4"/>
       <x:c r="AD20" s="4"/>
@@ -3359,7 +3360,7 @@
       <x:c r="AF20" s="4"/>
       <x:c r="AG20" s="4"/>
       <x:c r="AH20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:34">
@@ -3367,43 +3368,43 @@
       <x:c r="B21" s="4"/>
       <x:c r="C21" s="4"/>
       <x:c r="D21" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E21" s="4"/>
       <x:c r="F21" s="4"/>
       <x:c r="G21" s="4"/>
       <x:c r="H21" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I21" s="4"/>
       <x:c r="J21" s="4"/>
       <x:c r="K21" s="4"/>
       <x:c r="L21" s="4"/>
       <x:c r="M21" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="N21" s="4"/>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
       <x:c r="Q21" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="R21" s="4"/>
       <x:c r="S21" s="4"/>
       <x:c r="T21" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="U21" s="4"/>
       <x:c r="V21" s="4"/>
       <x:c r="W21" s="4"/>
       <x:c r="X21" s="4"/>
       <x:c r="Y21" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z21" s="4"/>
       <x:c r="AA21" s="4"/>
       <x:c r="AB21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC21" s="4"/>
       <x:c r="AD21" s="4"/>
@@ -3411,7 +3412,7 @@
       <x:c r="AF21" s="4"/>
       <x:c r="AG21" s="4"/>
       <x:c r="AH21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:34">
@@ -3419,43 +3420,43 @@
       <x:c r="B22" s="4"/>
       <x:c r="C22" s="4"/>
       <x:c r="D22" s="5" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E22" s="4"/>
       <x:c r="F22" s="4"/>
       <x:c r="G22" s="4"/>
       <x:c r="H22" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I22" s="4"/>
       <x:c r="J22" s="4"/>
       <x:c r="K22" s="4"/>
       <x:c r="L22" s="4"/>
       <x:c r="M22" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="N22" s="4"/>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="4"/>
       <x:c r="Q22" s="6" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R22" s="4"/>
       <x:c r="S22" s="4"/>
       <x:c r="T22" s="6" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="U22" s="4"/>
       <x:c r="V22" s="4"/>
       <x:c r="W22" s="4"/>
       <x:c r="X22" s="4"/>
       <x:c r="Y22" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z22" s="4"/>
       <x:c r="AA22" s="4"/>
       <x:c r="AB22" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC22" s="4"/>
       <x:c r="AD22" s="4"/>
@@ -3463,7 +3464,7 @@
       <x:c r="AF22" s="4"/>
       <x:c r="AG22" s="4"/>
       <x:c r="AH22" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:34">
@@ -3471,43 +3472,43 @@
       <x:c r="B23" s="4"/>
       <x:c r="C23" s="4"/>
       <x:c r="D23" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E23" s="4"/>
       <x:c r="F23" s="4"/>
       <x:c r="G23" s="4"/>
       <x:c r="H23" s="6" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I23" s="4"/>
       <x:c r="J23" s="4"/>
       <x:c r="K23" s="4"/>
       <x:c r="L23" s="4"/>
       <x:c r="M23" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="N23" s="4"/>
       <x:c r="O23" s="4"/>
       <x:c r="P23" s="4"/>
       <x:c r="Q23" s="6" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="R23" s="4"/>
       <x:c r="S23" s="4"/>
       <x:c r="T23" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="U23" s="4"/>
       <x:c r="V23" s="4"/>
       <x:c r="W23" s="4"/>
       <x:c r="X23" s="4"/>
       <x:c r="Y23" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z23" s="4"/>
       <x:c r="AA23" s="4"/>
       <x:c r="AB23" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC23" s="4"/>
       <x:c r="AD23" s="4"/>
@@ -3515,7 +3516,7 @@
       <x:c r="AF23" s="4"/>
       <x:c r="AG23" s="4"/>
       <x:c r="AH23" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:34">
@@ -3523,43 +3524,43 @@
       <x:c r="B24" s="4"/>
       <x:c r="C24" s="4"/>
       <x:c r="D24" s="5" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" s="4"/>
       <x:c r="F24" s="4"/>
       <x:c r="G24" s="4"/>
       <x:c r="H24" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I24" s="4"/>
       <x:c r="J24" s="4"/>
       <x:c r="K24" s="4"/>
       <x:c r="L24" s="4"/>
       <x:c r="M24" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="N24" s="4"/>
       <x:c r="O24" s="4"/>
       <x:c r="P24" s="4"/>
       <x:c r="Q24" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="R24" s="4"/>
       <x:c r="S24" s="4"/>
       <x:c r="T24" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="U24" s="4"/>
       <x:c r="V24" s="4"/>
       <x:c r="W24" s="4"/>
       <x:c r="X24" s="4"/>
       <x:c r="Y24" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z24" s="4"/>
       <x:c r="AA24" s="4"/>
       <x:c r="AB24" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC24" s="4"/>
       <x:c r="AD24" s="4"/>
@@ -3567,7 +3568,7 @@
       <x:c r="AF24" s="4"/>
       <x:c r="AG24" s="4"/>
       <x:c r="AH24" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:34">
@@ -3575,43 +3576,43 @@
       <x:c r="B25" s="4"/>
       <x:c r="C25" s="4"/>
       <x:c r="D25" s="5" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E25" s="4"/>
       <x:c r="F25" s="4"/>
       <x:c r="G25" s="4"/>
       <x:c r="H25" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="I25" s="4"/>
       <x:c r="J25" s="4"/>
       <x:c r="K25" s="4"/>
       <x:c r="L25" s="4"/>
       <x:c r="M25" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="N25" s="4"/>
       <x:c r="O25" s="4"/>
       <x:c r="P25" s="4"/>
       <x:c r="Q25" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="R25" s="4"/>
       <x:c r="S25" s="4"/>
       <x:c r="T25" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="U25" s="4"/>
       <x:c r="V25" s="4"/>
       <x:c r="W25" s="4"/>
       <x:c r="X25" s="4"/>
       <x:c r="Y25" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z25" s="4"/>
       <x:c r="AA25" s="4"/>
       <x:c r="AB25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC25" s="4"/>
       <x:c r="AD25" s="4"/>
@@ -3619,7 +3620,7 @@
       <x:c r="AF25" s="4"/>
       <x:c r="AG25" s="4"/>
       <x:c r="AH25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:34">
@@ -3627,43 +3628,43 @@
       <x:c r="B26" s="4"/>
       <x:c r="C26" s="4"/>
       <x:c r="D26" s="5" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E26" s="4"/>
       <x:c r="F26" s="4"/>
       <x:c r="G26" s="4"/>
       <x:c r="H26" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I26" s="4"/>
       <x:c r="J26" s="4"/>
       <x:c r="K26" s="4"/>
       <x:c r="L26" s="4"/>
       <x:c r="M26" s="6" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="N26" s="4"/>
       <x:c r="O26" s="4"/>
       <x:c r="P26" s="4"/>
       <x:c r="Q26" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="R26" s="4"/>
       <x:c r="S26" s="4"/>
       <x:c r="T26" s="6" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="U26" s="4"/>
       <x:c r="V26" s="4"/>
       <x:c r="W26" s="4"/>
       <x:c r="X26" s="4"/>
       <x:c r="Y26" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z26" s="4"/>
       <x:c r="AA26" s="4"/>
       <x:c r="AB26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC26" s="4"/>
       <x:c r="AD26" s="4"/>
@@ -3671,13 +3672,13 @@
       <x:c r="AF26" s="4"/>
       <x:c r="AG26" s="4"/>
       <x:c r="AH26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:34">
       <x:c r="A27" s="4"/>
       <x:c r="B27" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
@@ -3690,30 +3691,30 @@
       <x:c r="K27" s="4"/>
       <x:c r="L27" s="4"/>
       <x:c r="M27" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="N27" s="4"/>
       <x:c r="O27" s="4"/>
       <x:c r="P27" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q27" s="4"/>
       <x:c r="R27" s="4"/>
       <x:c r="S27" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="T27" s="4"/>
       <x:c r="U27" s="4"/>
       <x:c r="V27" s="4"/>
       <x:c r="W27" s="4"/>
       <x:c r="X27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y27" s="4"/>
       <x:c r="Z27" s="4"/>
       <x:c r="AA27" s="4"/>
       <x:c r="AB27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC27" s="4"/>
       <x:c r="AD27" s="4"/>
@@ -3721,13 +3722,13 @@
       <x:c r="AF27" s="4"/>
       <x:c r="AG27" s="4"/>
       <x:c r="AH27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:34">
       <x:c r="A28" s="4"/>
       <x:c r="B28" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C28" s="4"/>
       <x:c r="D28" s="4"/>
@@ -3765,7 +3766,7 @@
     <x:row r="29" spans="1:34">
       <x:c r="A29" s="4"/>
       <x:c r="B29" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C29" s="4"/>
       <x:c r="D29" s="4"/>
@@ -3773,7 +3774,7 @@
       <x:c r="F29" s="4"/>
       <x:c r="G29" s="4"/>
       <x:c r="H29" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I29" s="4"/>
       <x:c r="J29" s="4"/>
@@ -3807,43 +3808,43 @@
       <x:c r="B30" s="4"/>
       <x:c r="C30" s="4"/>
       <x:c r="D30" s="5" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E30" s="4"/>
       <x:c r="F30" s="4"/>
       <x:c r="G30" s="4"/>
       <x:c r="H30" s="6" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I30" s="4"/>
       <x:c r="J30" s="4"/>
       <x:c r="K30" s="4"/>
       <x:c r="L30" s="4"/>
       <x:c r="M30" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="N30" s="4"/>
       <x:c r="O30" s="4"/>
       <x:c r="P30" s="4"/>
       <x:c r="Q30" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="R30" s="4"/>
       <x:c r="S30" s="4"/>
       <x:c r="T30" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="U30" s="4"/>
       <x:c r="V30" s="4"/>
       <x:c r="W30" s="4"/>
       <x:c r="X30" s="4"/>
       <x:c r="Y30" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z30" s="4"/>
       <x:c r="AA30" s="4"/>
       <x:c r="AB30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC30" s="4"/>
       <x:c r="AD30" s="4"/>
@@ -3851,7 +3852,7 @@
       <x:c r="AF30" s="4"/>
       <x:c r="AG30" s="4"/>
       <x:c r="AH30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:34">
@@ -3859,43 +3860,43 @@
       <x:c r="B31" s="4"/>
       <x:c r="C31" s="4"/>
       <x:c r="D31" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E31" s="4"/>
       <x:c r="F31" s="4"/>
       <x:c r="G31" s="4"/>
       <x:c r="H31" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I31" s="4"/>
       <x:c r="J31" s="4"/>
       <x:c r="K31" s="4"/>
       <x:c r="L31" s="4"/>
       <x:c r="M31" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="N31" s="4"/>
       <x:c r="O31" s="4"/>
       <x:c r="P31" s="4"/>
       <x:c r="Q31" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="R31" s="4"/>
       <x:c r="S31" s="4"/>
       <x:c r="T31" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="U31" s="4"/>
       <x:c r="V31" s="4"/>
       <x:c r="W31" s="4"/>
       <x:c r="X31" s="4"/>
       <x:c r="Y31" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z31" s="4"/>
       <x:c r="AA31" s="4"/>
       <x:c r="AB31" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC31" s="4"/>
       <x:c r="AD31" s="4"/>
@@ -3903,7 +3904,7 @@
       <x:c r="AF31" s="4"/>
       <x:c r="AG31" s="4"/>
       <x:c r="AH31" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:34">
@@ -3911,43 +3912,43 @@
       <x:c r="B32" s="4"/>
       <x:c r="C32" s="4"/>
       <x:c r="D32" s="5" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E32" s="4"/>
       <x:c r="F32" s="4"/>
       <x:c r="G32" s="4"/>
       <x:c r="H32" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I32" s="4"/>
       <x:c r="J32" s="4"/>
       <x:c r="K32" s="4"/>
       <x:c r="L32" s="4"/>
       <x:c r="M32" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="N32" s="4"/>
       <x:c r="O32" s="4"/>
       <x:c r="P32" s="4"/>
       <x:c r="Q32" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="R32" s="4"/>
       <x:c r="S32" s="4"/>
       <x:c r="T32" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="U32" s="4"/>
       <x:c r="V32" s="4"/>
       <x:c r="W32" s="4"/>
       <x:c r="X32" s="4"/>
       <x:c r="Y32" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z32" s="4"/>
       <x:c r="AA32" s="4"/>
       <x:c r="AB32" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC32" s="4"/>
       <x:c r="AD32" s="4"/>
@@ -3955,7 +3956,7 @@
       <x:c r="AF32" s="4"/>
       <x:c r="AG32" s="4"/>
       <x:c r="AH32" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:34">
@@ -3963,43 +3964,43 @@
       <x:c r="B33" s="4"/>
       <x:c r="C33" s="4"/>
       <x:c r="D33" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E33" s="4"/>
       <x:c r="F33" s="4"/>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="I33" s="4"/>
       <x:c r="J33" s="4"/>
       <x:c r="K33" s="4"/>
       <x:c r="L33" s="4"/>
       <x:c r="M33" s="6" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="N33" s="4"/>
       <x:c r="O33" s="4"/>
       <x:c r="P33" s="4"/>
       <x:c r="Q33" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="R33" s="4"/>
       <x:c r="S33" s="4"/>
       <x:c r="T33" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="U33" s="4"/>
       <x:c r="V33" s="4"/>
       <x:c r="W33" s="4"/>
       <x:c r="X33" s="4"/>
       <x:c r="Y33" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z33" s="4"/>
       <x:c r="AA33" s="4"/>
       <x:c r="AB33" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC33" s="4"/>
       <x:c r="AD33" s="4"/>
@@ -4007,7 +4008,7 @@
       <x:c r="AF33" s="4"/>
       <x:c r="AG33" s="4"/>
       <x:c r="AH33" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:34">
@@ -4015,43 +4016,43 @@
       <x:c r="B34" s="4"/>
       <x:c r="C34" s="4"/>
       <x:c r="D34" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E34" s="4"/>
       <x:c r="F34" s="4"/>
       <x:c r="G34" s="4"/>
       <x:c r="H34" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I34" s="4"/>
       <x:c r="J34" s="4"/>
       <x:c r="K34" s="4"/>
       <x:c r="L34" s="4"/>
       <x:c r="M34" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="N34" s="4"/>
       <x:c r="O34" s="4"/>
       <x:c r="P34" s="4"/>
       <x:c r="Q34" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="R34" s="4"/>
       <x:c r="S34" s="4"/>
       <x:c r="T34" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="U34" s="4"/>
       <x:c r="V34" s="4"/>
       <x:c r="W34" s="4"/>
       <x:c r="X34" s="4"/>
       <x:c r="Y34" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z34" s="4"/>
       <x:c r="AA34" s="4"/>
       <x:c r="AB34" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC34" s="4"/>
       <x:c r="AD34" s="4"/>
@@ -4059,7 +4060,7 @@
       <x:c r="AF34" s="4"/>
       <x:c r="AG34" s="4"/>
       <x:c r="AH34" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:34">
@@ -4067,43 +4068,43 @@
       <x:c r="B35" s="4"/>
       <x:c r="C35" s="4"/>
       <x:c r="D35" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E35" s="4"/>
       <x:c r="F35" s="4"/>
       <x:c r="G35" s="4"/>
       <x:c r="H35" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I35" s="4"/>
       <x:c r="J35" s="4"/>
       <x:c r="K35" s="4"/>
       <x:c r="L35" s="4"/>
       <x:c r="M35" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="N35" s="4"/>
       <x:c r="O35" s="4"/>
       <x:c r="P35" s="4"/>
       <x:c r="Q35" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="R35" s="4"/>
       <x:c r="S35" s="4"/>
       <x:c r="T35" s="6" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="U35" s="4"/>
       <x:c r="V35" s="4"/>
       <x:c r="W35" s="4"/>
       <x:c r="X35" s="4"/>
       <x:c r="Y35" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z35" s="4"/>
       <x:c r="AA35" s="4"/>
       <x:c r="AB35" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC35" s="4"/>
       <x:c r="AD35" s="4"/>
@@ -4111,7 +4112,7 @@
       <x:c r="AF35" s="4"/>
       <x:c r="AG35" s="4"/>
       <x:c r="AH35" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:34">
@@ -4119,43 +4120,43 @@
       <x:c r="B36" s="4"/>
       <x:c r="C36" s="4"/>
       <x:c r="D36" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E36" s="4"/>
       <x:c r="F36" s="4"/>
       <x:c r="G36" s="4"/>
       <x:c r="H36" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="I36" s="4"/>
       <x:c r="J36" s="4"/>
       <x:c r="K36" s="4"/>
       <x:c r="L36" s="4"/>
       <x:c r="M36" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="N36" s="4"/>
       <x:c r="O36" s="4"/>
       <x:c r="P36" s="4"/>
       <x:c r="Q36" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="R36" s="4"/>
       <x:c r="S36" s="4"/>
       <x:c r="T36" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="U36" s="4"/>
       <x:c r="V36" s="4"/>
       <x:c r="W36" s="4"/>
       <x:c r="X36" s="4"/>
       <x:c r="Y36" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z36" s="4"/>
       <x:c r="AA36" s="4"/>
       <x:c r="AB36" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC36" s="4"/>
       <x:c r="AD36" s="4"/>
@@ -4163,7 +4164,7 @@
       <x:c r="AF36" s="4"/>
       <x:c r="AG36" s="4"/>
       <x:c r="AH36" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:34">
@@ -4171,43 +4172,43 @@
       <x:c r="B37" s="4"/>
       <x:c r="C37" s="4"/>
       <x:c r="D37" s="5" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E37" s="4"/>
       <x:c r="F37" s="4"/>
       <x:c r="G37" s="4"/>
       <x:c r="H37" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="I37" s="4"/>
       <x:c r="J37" s="4"/>
       <x:c r="K37" s="4"/>
       <x:c r="L37" s="4"/>
       <x:c r="M37" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="N37" s="4"/>
       <x:c r="O37" s="4"/>
       <x:c r="P37" s="4"/>
       <x:c r="Q37" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="R37" s="4"/>
       <x:c r="S37" s="4"/>
       <x:c r="T37" s="6" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="U37" s="4"/>
       <x:c r="V37" s="4"/>
       <x:c r="W37" s="4"/>
       <x:c r="X37" s="4"/>
       <x:c r="Y37" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z37" s="4"/>
       <x:c r="AA37" s="4"/>
       <x:c r="AB37" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC37" s="4"/>
       <x:c r="AD37" s="4"/>
@@ -4215,7 +4216,7 @@
       <x:c r="AF37" s="4"/>
       <x:c r="AG37" s="4"/>
       <x:c r="AH37" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:34">
@@ -4223,43 +4224,43 @@
       <x:c r="B38" s="4"/>
       <x:c r="C38" s="4"/>
       <x:c r="D38" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E38" s="4"/>
       <x:c r="F38" s="4"/>
       <x:c r="G38" s="4"/>
       <x:c r="H38" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="I38" s="4"/>
       <x:c r="J38" s="4"/>
       <x:c r="K38" s="4"/>
       <x:c r="L38" s="4"/>
       <x:c r="M38" s="6" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="N38" s="4"/>
       <x:c r="O38" s="4"/>
       <x:c r="P38" s="4"/>
       <x:c r="Q38" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="R38" s="4"/>
       <x:c r="S38" s="4"/>
       <x:c r="T38" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="U38" s="4"/>
       <x:c r="V38" s="4"/>
       <x:c r="W38" s="4"/>
       <x:c r="X38" s="4"/>
       <x:c r="Y38" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z38" s="4"/>
       <x:c r="AA38" s="4"/>
       <x:c r="AB38" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC38" s="4"/>
       <x:c r="AD38" s="4"/>
@@ -4267,7 +4268,7 @@
       <x:c r="AF38" s="4"/>
       <x:c r="AG38" s="4"/>
       <x:c r="AH38" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:34">
@@ -4275,43 +4276,43 @@
       <x:c r="B39" s="4"/>
       <x:c r="C39" s="4"/>
       <x:c r="D39" s="5" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E39" s="4"/>
       <x:c r="F39" s="4"/>
       <x:c r="G39" s="4"/>
       <x:c r="H39" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I39" s="4"/>
       <x:c r="J39" s="4"/>
       <x:c r="K39" s="4"/>
       <x:c r="L39" s="4"/>
       <x:c r="M39" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="N39" s="4"/>
       <x:c r="O39" s="4"/>
       <x:c r="P39" s="4"/>
       <x:c r="Q39" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="R39" s="4"/>
       <x:c r="S39" s="4"/>
       <x:c r="T39" s="6" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="U39" s="4"/>
       <x:c r="V39" s="4"/>
       <x:c r="W39" s="4"/>
       <x:c r="X39" s="4"/>
       <x:c r="Y39" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z39" s="4"/>
       <x:c r="AA39" s="4"/>
       <x:c r="AB39" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC39" s="4"/>
       <x:c r="AD39" s="4"/>
@@ -4319,7 +4320,7 @@
       <x:c r="AF39" s="4"/>
       <x:c r="AG39" s="4"/>
       <x:c r="AH39" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:34">
@@ -4327,43 +4328,43 @@
       <x:c r="B40" s="4"/>
       <x:c r="C40" s="4"/>
       <x:c r="D40" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E40" s="4"/>
       <x:c r="F40" s="4"/>
       <x:c r="G40" s="4"/>
       <x:c r="H40" s="6" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I40" s="4"/>
       <x:c r="J40" s="4"/>
       <x:c r="K40" s="4"/>
       <x:c r="L40" s="4"/>
       <x:c r="M40" s="6" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="N40" s="4"/>
       <x:c r="O40" s="4"/>
       <x:c r="P40" s="4"/>
       <x:c r="Q40" s="6" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="R40" s="4"/>
       <x:c r="S40" s="4"/>
       <x:c r="T40" s="6" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="U40" s="4"/>
       <x:c r="V40" s="4"/>
       <x:c r="W40" s="4"/>
       <x:c r="X40" s="4"/>
       <x:c r="Y40" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z40" s="4"/>
       <x:c r="AA40" s="4"/>
       <x:c r="AB40" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC40" s="4"/>
       <x:c r="AD40" s="4"/>
@@ -4371,7 +4372,7 @@
       <x:c r="AF40" s="4"/>
       <x:c r="AG40" s="4"/>
       <x:c r="AH40" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:34">
@@ -4379,43 +4380,43 @@
       <x:c r="B41" s="4"/>
       <x:c r="C41" s="4"/>
       <x:c r="D41" s="5" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="E41" s="4"/>
       <x:c r="F41" s="4"/>
       <x:c r="G41" s="4"/>
       <x:c r="H41" s="6" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="I41" s="4"/>
       <x:c r="J41" s="4"/>
       <x:c r="K41" s="4"/>
       <x:c r="L41" s="4"/>
       <x:c r="M41" s="6" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="N41" s="4"/>
       <x:c r="O41" s="4"/>
       <x:c r="P41" s="6" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="Q41" s="4"/>
       <x:c r="R41" s="4"/>
       <x:c r="S41" s="4"/>
       <x:c r="T41" s="6" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="U41" s="4"/>
       <x:c r="V41" s="4"/>
       <x:c r="W41" s="4"/>
       <x:c r="X41" s="4"/>
       <x:c r="Y41" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z41" s="4"/>
       <x:c r="AA41" s="4"/>
       <x:c r="AB41" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC41" s="4"/>
       <x:c r="AD41" s="4"/>
@@ -4423,13 +4424,13 @@
       <x:c r="AF41" s="4"/>
       <x:c r="AG41" s="4"/>
       <x:c r="AH41" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:34">
       <x:c r="A42" s="4"/>
       <x:c r="B42" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C42" s="4"/>
       <x:c r="D42" s="4"/>
@@ -4442,30 +4443,30 @@
       <x:c r="K42" s="4"/>
       <x:c r="L42" s="4"/>
       <x:c r="M42" s="6" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="N42" s="4"/>
       <x:c r="O42" s="4"/>
       <x:c r="P42" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="Q42" s="4"/>
       <x:c r="R42" s="4"/>
       <x:c r="S42" s="4"/>
       <x:c r="T42" s="6" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="U42" s="4"/>
       <x:c r="V42" s="4"/>
       <x:c r="W42" s="4"/>
       <x:c r="X42" s="4"/>
       <x:c r="Y42" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z42" s="4"/>
       <x:c r="AA42" s="4"/>
       <x:c r="AB42" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC42" s="4"/>
       <x:c r="AD42" s="4"/>
@@ -4473,7 +4474,7 @@
       <x:c r="AF42" s="4"/>
       <x:c r="AG42" s="4"/>
       <x:c r="AH42" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:34">
@@ -4484,43 +4485,43 @@
       <x:c r="E43" s="4"/>
       <x:c r="F43" s="4"/>
       <x:c r="G43" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H43" s="4"/>
       <x:c r="I43" s="4"/>
       <x:c r="J43" s="4"/>
       <x:c r="K43" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L43" s="4"/>
       <x:c r="M43" s="4"/>
       <x:c r="N43" s="4"/>
       <x:c r="O43" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P43" s="4"/>
       <x:c r="Q43" s="4"/>
       <x:c r="R43" s="4"/>
       <x:c r="S43" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T43" s="4"/>
       <x:c r="U43" s="4"/>
       <x:c r="V43" s="4"/>
       <x:c r="W43" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="X43" s="4"/>
       <x:c r="Y43" s="4"/>
       <x:c r="Z43" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AA43" s="4"/>
       <x:c r="AB43" s="4"/>
       <x:c r="AC43" s="4"/>
       <x:c r="AD43" s="4"/>
       <x:c r="AE43" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AF43" s="4"/>
       <x:c r="AG43" s="4"/>
@@ -4530,13 +4531,13 @@
       <x:c r="A44" s="4"/>
       <x:c r="B44" s="4"/>
       <x:c r="C44" s="5" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D44" s="4"/>
       <x:c r="E44" s="4"/>
       <x:c r="F44" s="4"/>
       <x:c r="G44" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H44" s="4"/>
       <x:c r="I44" s="4"/>
@@ -4544,34 +4545,34 @@
       <x:c r="K44" s="4"/>
       <x:c r="L44" s="4"/>
       <x:c r="M44" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="N44" s="4"/>
       <x:c r="O44" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="P44" s="4"/>
       <x:c r="Q44" s="4"/>
       <x:c r="R44" s="4"/>
       <x:c r="S44" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="T44" s="4"/>
       <x:c r="U44" s="4"/>
       <x:c r="V44" s="4"/>
       <x:c r="W44" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="X44" s="4"/>
       <x:c r="Y44" s="4"/>
       <x:c r="Z44" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="AA44" s="4"/>
       <x:c r="AB44" s="4"/>
       <x:c r="AC44" s="4"/>
       <x:c r="AD44" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="AE44" s="4"/>
       <x:c r="AF44" s="4"/>
@@ -4600,7 +4601,7 @@
       <x:c r="S45" s="4"/>
       <x:c r="T45" s="4"/>
       <x:c r="U45" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="V45" s="4"/>
       <x:c r="W45" s="4"/>
@@ -4608,7 +4609,7 @@
       <x:c r="Y45" s="4"/>
       <x:c r="Z45" s="4"/>
       <x:c r="AA45" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AB45" s="4"/>
       <x:c r="AC45" s="4"/>
@@ -4617,13 +4618,13 @@
       <x:c r="AF45" s="4"/>
       <x:c r="AG45" s="4"/>
       <x:c r="AH45" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:34">
       <x:c r="A46" s="4"/>
       <x:c r="B46" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C46" s="4"/>
       <x:c r="D46" s="4"/>
@@ -4661,7 +4662,7 @@
     <x:row r="47" spans="1:34">
       <x:c r="A47" s="4"/>
       <x:c r="B47" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C47" s="4"/>
       <x:c r="D47" s="4"/>
@@ -4669,7 +4670,7 @@
       <x:c r="F47" s="4"/>
       <x:c r="G47" s="4"/>
       <x:c r="H47" s="6" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="I47" s="4"/>
       <x:c r="J47" s="4"/>
@@ -4703,43 +4704,43 @@
       <x:c r="B48" s="4"/>
       <x:c r="C48" s="4"/>
       <x:c r="D48" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E48" s="4"/>
       <x:c r="F48" s="4"/>
       <x:c r="G48" s="4"/>
       <x:c r="H48" s="6" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="I48" s="4"/>
       <x:c r="J48" s="4"/>
       <x:c r="K48" s="4"/>
       <x:c r="L48" s="4"/>
       <x:c r="M48" s="6" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="N48" s="4"/>
       <x:c r="O48" s="4"/>
       <x:c r="P48" s="6" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="Q48" s="4"/>
       <x:c r="R48" s="4"/>
       <x:c r="S48" s="4"/>
       <x:c r="T48" s="6" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="U48" s="4"/>
       <x:c r="V48" s="4"/>
       <x:c r="W48" s="4"/>
       <x:c r="X48" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y48" s="4"/>
       <x:c r="Z48" s="4"/>
       <x:c r="AA48" s="4"/>
       <x:c r="AB48" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC48" s="4"/>
       <x:c r="AD48" s="4"/>
@@ -4747,7 +4748,7 @@
       <x:c r="AF48" s="4"/>
       <x:c r="AG48" s="4"/>
       <x:c r="AH48" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:34">
@@ -4755,43 +4756,43 @@
       <x:c r="B49" s="4"/>
       <x:c r="C49" s="4"/>
       <x:c r="D49" s="5" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E49" s="4"/>
       <x:c r="F49" s="4"/>
       <x:c r="G49" s="4"/>
       <x:c r="H49" s="6" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="I49" s="4"/>
       <x:c r="J49" s="4"/>
       <x:c r="K49" s="4"/>
       <x:c r="L49" s="4"/>
       <x:c r="M49" s="6" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="N49" s="4"/>
       <x:c r="O49" s="4"/>
       <x:c r="P49" s="6" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="Q49" s="4"/>
       <x:c r="R49" s="4"/>
       <x:c r="S49" s="4"/>
       <x:c r="T49" s="6" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="U49" s="4"/>
       <x:c r="V49" s="4"/>
       <x:c r="W49" s="4"/>
       <x:c r="X49" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y49" s="4"/>
       <x:c r="Z49" s="4"/>
       <x:c r="AA49" s="4"/>
       <x:c r="AB49" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC49" s="4"/>
       <x:c r="AD49" s="4"/>
@@ -4799,7 +4800,7 @@
       <x:c r="AF49" s="4"/>
       <x:c r="AG49" s="4"/>
       <x:c r="AH49" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:34">
@@ -4807,43 +4808,43 @@
       <x:c r="B50" s="4"/>
       <x:c r="C50" s="4"/>
       <x:c r="D50" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E50" s="4"/>
       <x:c r="F50" s="4"/>
       <x:c r="G50" s="4"/>
       <x:c r="H50" s="6" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="I50" s="4"/>
       <x:c r="J50" s="4"/>
       <x:c r="K50" s="4"/>
       <x:c r="L50" s="4"/>
       <x:c r="M50" s="6" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="N50" s="4"/>
       <x:c r="O50" s="4"/>
       <x:c r="P50" s="6" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="Q50" s="4"/>
       <x:c r="R50" s="4"/>
       <x:c r="S50" s="4"/>
       <x:c r="T50" s="6" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="U50" s="4"/>
       <x:c r="V50" s="4"/>
       <x:c r="W50" s="4"/>
       <x:c r="X50" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y50" s="4"/>
       <x:c r="Z50" s="4"/>
       <x:c r="AA50" s="4"/>
       <x:c r="AB50" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC50" s="4"/>
       <x:c r="AD50" s="4"/>
@@ -4851,7 +4852,7 @@
       <x:c r="AF50" s="4"/>
       <x:c r="AG50" s="4"/>
       <x:c r="AH50" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:34">
@@ -4859,43 +4860,43 @@
       <x:c r="B51" s="4"/>
       <x:c r="C51" s="4"/>
       <x:c r="D51" s="5" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="E51" s="4"/>
       <x:c r="F51" s="4"/>
       <x:c r="G51" s="4"/>
       <x:c r="H51" s="6" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="I51" s="4"/>
       <x:c r="J51" s="4"/>
       <x:c r="K51" s="4"/>
       <x:c r="L51" s="4"/>
       <x:c r="M51" s="6" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="N51" s="4"/>
       <x:c r="O51" s="4"/>
       <x:c r="P51" s="6" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="Q51" s="4"/>
       <x:c r="R51" s="4"/>
       <x:c r="S51" s="4"/>
       <x:c r="T51" s="6" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="U51" s="4"/>
       <x:c r="V51" s="4"/>
       <x:c r="W51" s="4"/>
       <x:c r="X51" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y51" s="4"/>
       <x:c r="Z51" s="4"/>
       <x:c r="AA51" s="4"/>
       <x:c r="AB51" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC51" s="4"/>
       <x:c r="AD51" s="4"/>
@@ -4903,7 +4904,7 @@
       <x:c r="AF51" s="4"/>
       <x:c r="AG51" s="4"/>
       <x:c r="AH51" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:34">
@@ -4911,43 +4912,43 @@
       <x:c r="B52" s="4"/>
       <x:c r="C52" s="4"/>
       <x:c r="D52" s="5" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="E52" s="4"/>
       <x:c r="F52" s="4"/>
       <x:c r="G52" s="4"/>
       <x:c r="H52" s="6" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="I52" s="4"/>
       <x:c r="J52" s="4"/>
       <x:c r="K52" s="4"/>
       <x:c r="L52" s="4"/>
       <x:c r="M52" s="6" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="N52" s="4"/>
       <x:c r="O52" s="4"/>
       <x:c r="P52" s="6" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Q52" s="4"/>
       <x:c r="R52" s="4"/>
       <x:c r="S52" s="4"/>
       <x:c r="T52" s="6" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="U52" s="4"/>
       <x:c r="V52" s="4"/>
       <x:c r="W52" s="4"/>
       <x:c r="X52" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y52" s="4"/>
       <x:c r="Z52" s="4"/>
       <x:c r="AA52" s="4"/>
       <x:c r="AB52" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC52" s="4"/>
       <x:c r="AD52" s="4"/>
@@ -4955,7 +4956,7 @@
       <x:c r="AF52" s="4"/>
       <x:c r="AG52" s="4"/>
       <x:c r="AH52" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:34">
@@ -4963,43 +4964,43 @@
       <x:c r="B53" s="4"/>
       <x:c r="C53" s="4"/>
       <x:c r="D53" s="5" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E53" s="4"/>
       <x:c r="F53" s="4"/>
       <x:c r="G53" s="4"/>
       <x:c r="H53" s="6" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="I53" s="4"/>
       <x:c r="J53" s="4"/>
       <x:c r="K53" s="4"/>
       <x:c r="L53" s="4"/>
       <x:c r="M53" s="6" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="N53" s="4"/>
       <x:c r="O53" s="4"/>
       <x:c r="P53" s="6" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="Q53" s="4"/>
       <x:c r="R53" s="4"/>
       <x:c r="S53" s="4"/>
       <x:c r="T53" s="6" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="U53" s="4"/>
       <x:c r="V53" s="4"/>
       <x:c r="W53" s="4"/>
       <x:c r="X53" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y53" s="4"/>
       <x:c r="Z53" s="4"/>
       <x:c r="AA53" s="4"/>
       <x:c r="AB53" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC53" s="4"/>
       <x:c r="AD53" s="4"/>
@@ -5007,7 +5008,7 @@
       <x:c r="AF53" s="4"/>
       <x:c r="AG53" s="4"/>
       <x:c r="AH53" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:34">
@@ -5015,43 +5016,43 @@
       <x:c r="B54" s="4"/>
       <x:c r="C54" s="4"/>
       <x:c r="D54" s="5" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E54" s="4"/>
       <x:c r="F54" s="4"/>
       <x:c r="G54" s="4"/>
       <x:c r="H54" s="6" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="I54" s="4"/>
       <x:c r="J54" s="4"/>
       <x:c r="K54" s="4"/>
       <x:c r="L54" s="4"/>
       <x:c r="M54" s="6" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="N54" s="4"/>
       <x:c r="O54" s="4"/>
       <x:c r="P54" s="6" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="Q54" s="4"/>
       <x:c r="R54" s="4"/>
       <x:c r="S54" s="4"/>
       <x:c r="T54" s="6" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="U54" s="4"/>
       <x:c r="V54" s="4"/>
       <x:c r="W54" s="4"/>
       <x:c r="X54" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Y54" s="4"/>
       <x:c r="Z54" s="4"/>
       <x:c r="AA54" s="4"/>
       <x:c r="AB54" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AC54" s="4"/>
       <x:c r="AD54" s="4"/>
@@ -5059,7 +5060,7 @@
       <x:c r="AF54" s="4"/>
       <x:c r="AG54" s="4"/>
       <x:c r="AH54" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:34">
@@ -5067,42 +5068,42 @@
       <x:c r="B55" s="4"/>
       <x:c r="C55" s="4"/>
       <x:c r="D55" s="5" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E55" s="4"/>
       <x:c r="F55" s="4"/>
       <x:c r="G55" s="4"/>
       <x:c r="H55" s="6" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="I55" s="4"/>
       <x:c r="J55" s="4"/>
       <x:c r="K55" s="4"/>
       <x:c r="L55" s="4"/>
       <x:c r="M55" s="6" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="N55" s="4"/>
       <x:c r="O55" s="4"/>
       <x:c r="P55" s="6" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="Q55" s="4"/>
       <x:c r="R55" s="4"/>
       <x:c r="S55" s="4"/>
       <x:c r="T55" s="6" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="U55" s="4"/>
       <x:c r="V55" s="4"/>
       <x:c r="W55" s="4"/>
       <x:c r="X55" s="6" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="Y55" s="4"/>
       <x:c r="Z55" s="4"/>
       <x:c r="AA55" s="6" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="AB55" s="4"/>
       <x:c r="AC55" s="4"/>
@@ -5110,7 +5111,7 @@
       <x:c r="AE55" s="4"/>
       <x:c r="AF55" s="4"/>
       <x:c r="AG55" s="6" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="AH55" s="4"/>
     </x:row>
@@ -5119,13 +5120,13 @@
       <x:c r="B56" s="4"/>
       <x:c r="C56" s="4"/>
       <x:c r="D56" s="5" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="E56" s="4"/>
       <x:c r="F56" s="4"/>
       <x:c r="G56" s="4"/>
       <x:c r="H56" s="6" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="I56" s="4"/>
       <x:c r="J56" s="4"/>
@@ -5133,28 +5134,28 @@
       <x:c r="L56" s="4"/>
       <x:c r="M56" s="4"/>
       <x:c r="N56" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O56" s="4"/>
       <x:c r="P56" s="4"/>
       <x:c r="Q56" s="4"/>
       <x:c r="R56" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S56" s="4"/>
       <x:c r="T56" s="4"/>
       <x:c r="U56" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="V56" s="4"/>
       <x:c r="W56" s="4"/>
       <x:c r="X56" s="6" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="Y56" s="4"/>
       <x:c r="Z56" s="4"/>
       <x:c r="AA56" s="6" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="AB56" s="4"/>
       <x:c r="AC56" s="4"/>
@@ -5162,14 +5163,14 @@
       <x:c r="AE56" s="4"/>
       <x:c r="AF56" s="4"/>
       <x:c r="AG56" s="6" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="AH56" s="4"/>
     </x:row>
     <x:row r="57" spans="1:34">
       <x:c r="A57" s="4"/>
       <x:c r="B57" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C57" s="4"/>
       <x:c r="D57" s="4"/>
@@ -5182,29 +5183,29 @@
       <x:c r="K57" s="4"/>
       <x:c r="L57" s="4"/>
       <x:c r="M57" s="6" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="N57" s="4"/>
       <x:c r="O57" s="4"/>
       <x:c r="P57" s="6" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="Q57" s="4"/>
       <x:c r="R57" s="4"/>
       <x:c r="S57" s="4"/>
       <x:c r="T57" s="6" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="U57" s="4"/>
       <x:c r="V57" s="4"/>
       <x:c r="W57" s="4"/>
       <x:c r="X57" s="6" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="Y57" s="4"/>
       <x:c r="Z57" s="4"/>
       <x:c r="AA57" s="6" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="AB57" s="4"/>
       <x:c r="AC57" s="4"/>
@@ -5212,14 +5213,14 @@
       <x:c r="AE57" s="4"/>
       <x:c r="AF57" s="4"/>
       <x:c r="AG57" s="6" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="AH57" s="4"/>
     </x:row>
     <x:row r="58" spans="1:34">
       <x:c r="A58" s="4"/>
       <x:c r="B58" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C58" s="4"/>
       <x:c r="D58" s="4"/>
@@ -5232,17 +5233,17 @@
       <x:c r="K58" s="4"/>
       <x:c r="L58" s="4"/>
       <x:c r="M58" s="6" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="N58" s="4"/>
       <x:c r="O58" s="4"/>
       <x:c r="P58" s="6" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="Q58" s="4"/>
       <x:c r="R58" s="4"/>
       <x:c r="S58" s="6" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="T58" s="4"/>
       <x:c r="U58" s="4"/>
@@ -5262,22 +5263,22 @@
     </x:row>
     <x:row r="59" spans="1:34">
       <x:c r="A59" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B59" s="4"/>
       <x:c r="C59" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D59" s="4"/>
       <x:c r="E59" s="4"/>
       <x:c r="F59" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G59" s="4"/>
       <x:c r="H59" s="4"/>
       <x:c r="I59" s="4"/>
       <x:c r="J59" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="K59" s="4"/>
       <x:c r="L59" s="4"/>
@@ -5301,13 +5302,13 @@
       <x:c r="AD59" s="4"/>
       <x:c r="AE59" s="4"/>
       <x:c r="AF59" s="5" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="AG59" s="4"/>
       <x:c r="AH59" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1"/>
+  <x:sheetProtection password="8CAE" sheet="1" objects="1"/>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AH1"/>
     <x:mergeCell ref="A2:AH2"/>
@@ -5359,7 +5360,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:28" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -5391,7 +5392,7 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -5424,12 +5425,12 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="4"/>
       <x:c r="B3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
       <x:c r="E3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F3" s="4"/>
       <x:c r="G3" s="4"/>
@@ -5442,7 +5443,7 @@
       <x:c r="N3" s="4"/>
       <x:c r="O3" s="4"/>
       <x:c r="P3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q3" s="4"/>
       <x:c r="R3" s="4"/>
@@ -5451,7 +5452,7 @@
       <x:c r="U3" s="4"/>
       <x:c r="V3" s="4"/>
       <x:c r="W3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X3" s="4"/>
       <x:c r="Y3" s="4"/>
@@ -5462,7 +5463,7 @@
     <x:row r="4" spans="1:28">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -5470,7 +5471,7 @@
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -5480,7 +5481,7 @@
       <x:c r="N4" s="4"/>
       <x:c r="O4" s="4"/>
       <x:c r="P4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="Q4" s="4"/>
       <x:c r="R4" s="4"/>
@@ -5490,7 +5491,7 @@
       <x:c r="V4" s="4"/>
       <x:c r="W4" s="4"/>
       <x:c r="X4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="Y4" s="4"/>
       <x:c r="Z4" s="4"/>
@@ -5500,7 +5501,7 @@
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -5508,7 +5509,7 @@
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -5518,7 +5519,7 @@
       <x:c r="N5" s="4"/>
       <x:c r="O5" s="4"/>
       <x:c r="P5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="Q5" s="4"/>
       <x:c r="R5" s="4"/>
@@ -5527,7 +5528,7 @@
       <x:c r="U5" s="4"/>
       <x:c r="V5" s="4"/>
       <x:c r="W5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="X5" s="4"/>
       <x:c r="Y5" s="4"/>
@@ -5538,7 +5539,7 @@
     <x:row r="6" spans="1:28">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -5546,7 +5547,7 @@
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="J6" s="4"/>
@@ -5556,7 +5557,7 @@
       <x:c r="N6" s="4"/>
       <x:c r="O6" s="4"/>
       <x:c r="P6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="Q6" s="4"/>
       <x:c r="R6" s="4"/>
@@ -5567,7 +5568,7 @@
       <x:c r="W6" s="4"/>
       <x:c r="X6" s="4"/>
       <x:c r="Y6" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="Z6" s="4"/>
       <x:c r="AA6" s="4"/>
@@ -5576,13 +5577,13 @@
     <x:row r="7" spans="1:28">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
@@ -5594,7 +5595,7 @@
       <x:c r="N7" s="4"/>
       <x:c r="O7" s="4"/>
       <x:c r="P7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Q7" s="4"/>
       <x:c r="R7" s="4"/>
@@ -5605,7 +5606,7 @@
       <x:c r="W7" s="4"/>
       <x:c r="X7" s="4"/>
       <x:c r="Y7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="Z7" s="4"/>
       <x:c r="AA7" s="4"/>
@@ -5614,11 +5615,11 @@
     <x:row r="8" spans="1:28">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
@@ -5640,7 +5641,7 @@
       <x:c r="V8" s="4"/>
       <x:c r="W8" s="4"/>
       <x:c r="X8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="Y8" s="4"/>
       <x:c r="Z8" s="4"/>
@@ -5660,7 +5661,7 @@
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="5" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="M9" s="4"/>
       <x:c r="N9" s="4"/>
@@ -5692,7 +5693,7 @@
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
       <x:c r="L10" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M10" s="4"/>
       <x:c r="N10" s="4"/>
@@ -5727,7 +5728,7 @@
       <x:c r="M11" s="4"/>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="4"/>
@@ -5753,27 +5754,27 @@
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="N12" s="4"/>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="Q12" s="4"/>
       <x:c r="R12" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S12" s="4"/>
       <x:c r="T12" s="4"/>
       <x:c r="U12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="V12" s="4"/>
       <x:c r="W12" s="4"/>
@@ -5781,7 +5782,7 @@
       <x:c r="Y12" s="4"/>
       <x:c r="Z12" s="4"/>
       <x:c r="AA12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AB12" s="4"/>
     </x:row>
@@ -5790,33 +5791,33 @@
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="J13" s="4"/>
       <x:c r="K13" s="4"/>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="N13" s="4"/>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="Q13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="4"/>
       <x:c r="T13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="U13" s="4"/>
       <x:c r="V13" s="4"/>
@@ -5824,7 +5825,7 @@
       <x:c r="X13" s="4"/>
       <x:c r="Y13" s="4"/>
       <x:c r="Z13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AA13" s="4"/>
       <x:c r="AB13" s="4"/>
@@ -5843,19 +5844,19 @@
       <x:c r="K14" s="4"/>
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="Q14" s="4"/>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4"/>
       <x:c r="T14" s="4"/>
       <x:c r="U14" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="V14" s="4"/>
       <x:c r="W14" s="4"/>
@@ -5863,14 +5864,14 @@
       <x:c r="Y14" s="4"/>
       <x:c r="Z14" s="4"/>
       <x:c r="AA14" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AB14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:28">
       <x:c r="A15" s="4"/>
       <x:c r="B15" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -5880,27 +5881,27 @@
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="6" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="K15" s="4"/>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="6" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="N15" s="4"/>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="6" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T15" s="4"/>
       <x:c r="U15" s="4"/>
       <x:c r="V15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W15" s="4"/>
       <x:c r="X15" s="4"/>
@@ -5908,13 +5909,13 @@
       <x:c r="Z15" s="4"/>
       <x:c r="AA15" s="4"/>
       <x:c r="AB15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28">
       <x:c r="A16" s="4"/>
       <x:c r="B16" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
@@ -5924,27 +5925,27 @@
       <x:c r="H16" s="4"/>
       <x:c r="I16" s="4"/>
       <x:c r="J16" s="6" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="K16" s="4"/>
       <x:c r="L16" s="4"/>
       <x:c r="M16" s="6" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="6" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="Q16" s="4"/>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T16" s="4"/>
       <x:c r="U16" s="4"/>
       <x:c r="V16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W16" s="4"/>
       <x:c r="X16" s="4"/>
@@ -5952,13 +5953,13 @@
       <x:c r="Z16" s="4"/>
       <x:c r="AA16" s="4"/>
       <x:c r="AB16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28">
       <x:c r="A17" s="4"/>
       <x:c r="B17" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="4"/>
@@ -5968,27 +5969,27 @@
       <x:c r="H17" s="4"/>
       <x:c r="I17" s="4"/>
       <x:c r="J17" s="6" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="K17" s="4"/>
       <x:c r="L17" s="4"/>
       <x:c r="M17" s="6" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="N17" s="4"/>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="6" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="Q17" s="4"/>
       <x:c r="R17" s="4"/>
       <x:c r="S17" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T17" s="4"/>
       <x:c r="U17" s="4"/>
       <x:c r="V17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W17" s="4"/>
       <x:c r="X17" s="4"/>
@@ -5996,13 +5997,13 @@
       <x:c r="Z17" s="4"/>
       <x:c r="AA17" s="4"/>
       <x:c r="AB17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28">
       <x:c r="A18" s="4"/>
       <x:c r="B18" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="4"/>
@@ -6012,27 +6013,27 @@
       <x:c r="H18" s="4"/>
       <x:c r="I18" s="4"/>
       <x:c r="J18" s="6" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="K18" s="4"/>
       <x:c r="L18" s="4"/>
       <x:c r="M18" s="4"/>
       <x:c r="N18" s="6" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="6" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="Q18" s="4"/>
       <x:c r="R18" s="4"/>
       <x:c r="S18" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T18" s="4"/>
       <x:c r="U18" s="4"/>
       <x:c r="V18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W18" s="4"/>
       <x:c r="X18" s="4"/>
@@ -6040,13 +6041,13 @@
       <x:c r="Z18" s="4"/>
       <x:c r="AA18" s="4"/>
       <x:c r="AB18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:28">
       <x:c r="A19" s="4"/>
       <x:c r="B19" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C19" s="4"/>
       <x:c r="D19" s="4"/>
@@ -6056,27 +6057,27 @@
       <x:c r="H19" s="4"/>
       <x:c r="I19" s="4"/>
       <x:c r="J19" s="6" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="K19" s="4"/>
       <x:c r="L19" s="4"/>
       <x:c r="M19" s="6" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="N19" s="4"/>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="6" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="Q19" s="4"/>
       <x:c r="R19" s="4"/>
       <x:c r="S19" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T19" s="4"/>
       <x:c r="U19" s="4"/>
       <x:c r="V19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W19" s="4"/>
       <x:c r="X19" s="4"/>
@@ -6084,13 +6085,13 @@
       <x:c r="Z19" s="4"/>
       <x:c r="AA19" s="4"/>
       <x:c r="AB19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:28">
       <x:c r="A20" s="4"/>
       <x:c r="B20" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C20" s="4"/>
       <x:c r="D20" s="4"/>
@@ -6100,27 +6101,27 @@
       <x:c r="H20" s="4"/>
       <x:c r="I20" s="4"/>
       <x:c r="J20" s="6" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="K20" s="4"/>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="6" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N20" s="4"/>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="Q20" s="4"/>
       <x:c r="R20" s="4"/>
       <x:c r="S20" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T20" s="4"/>
       <x:c r="U20" s="4"/>
       <x:c r="V20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W20" s="4"/>
       <x:c r="X20" s="4"/>
@@ -6128,7 +6129,7 @@
       <x:c r="Z20" s="4"/>
       <x:c r="AA20" s="4"/>
       <x:c r="AB20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:28">
@@ -6146,7 +6147,7 @@
       <x:c r="L21" s="4"/>
       <x:c r="M21" s="4"/>
       <x:c r="N21" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
@@ -6173,27 +6174,27 @@
       <x:c r="G22" s="4"/>
       <x:c r="H22" s="4"/>
       <x:c r="I22" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J22" s="4"/>
       <x:c r="K22" s="4"/>
       <x:c r="L22" s="4"/>
       <x:c r="M22" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="N22" s="4"/>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="Q22" s="4"/>
       <x:c r="R22" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S22" s="4"/>
       <x:c r="T22" s="4"/>
       <x:c r="U22" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="V22" s="4"/>
       <x:c r="W22" s="4"/>
@@ -6201,7 +6202,7 @@
       <x:c r="Y22" s="4"/>
       <x:c r="Z22" s="4"/>
       <x:c r="AA22" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AB22" s="4"/>
     </x:row>
@@ -6210,40 +6211,40 @@
       <x:c r="B23" s="4"/>
       <x:c r="C23" s="4"/>
       <x:c r="D23" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E23" s="4"/>
       <x:c r="F23" s="4"/>
       <x:c r="G23" s="4"/>
       <x:c r="H23" s="4"/>
       <x:c r="I23" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="J23" s="4"/>
       <x:c r="K23" s="4"/>
       <x:c r="L23" s="4"/>
       <x:c r="M23" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="N23" s="4"/>
       <x:c r="O23" s="4"/>
       <x:c r="P23" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="Q23" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="R23" s="4"/>
       <x:c r="S23" s="4"/>
       <x:c r="T23" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="U23" s="4"/>
       <x:c r="V23" s="4"/>
       <x:c r="W23" s="4"/>
       <x:c r="X23" s="4"/>
       <x:c r="Y23" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="Z23" s="4"/>
       <x:c r="AA23" s="4"/>
@@ -6263,19 +6264,19 @@
       <x:c r="K24" s="4"/>
       <x:c r="L24" s="4"/>
       <x:c r="M24" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N24" s="4"/>
       <x:c r="O24" s="4"/>
       <x:c r="P24" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="Q24" s="4"/>
       <x:c r="R24" s="4"/>
       <x:c r="S24" s="4"/>
       <x:c r="T24" s="4"/>
       <x:c r="U24" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="V24" s="4"/>
       <x:c r="W24" s="4"/>
@@ -6283,14 +6284,14 @@
       <x:c r="Y24" s="4"/>
       <x:c r="Z24" s="4"/>
       <x:c r="AA24" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AB24" s="4"/>
     </x:row>
     <x:row r="25" spans="1:28">
       <x:c r="A25" s="4"/>
       <x:c r="B25" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C25" s="4"/>
       <x:c r="D25" s="4"/>
@@ -6300,27 +6301,27 @@
       <x:c r="H25" s="4"/>
       <x:c r="I25" s="4"/>
       <x:c r="J25" s="6" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="K25" s="4"/>
       <x:c r="L25" s="4"/>
       <x:c r="M25" s="6" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="N25" s="4"/>
       <x:c r="O25" s="4"/>
       <x:c r="P25" s="6" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="Q25" s="4"/>
       <x:c r="R25" s="4"/>
       <x:c r="S25" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T25" s="4"/>
       <x:c r="U25" s="4"/>
       <x:c r="V25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W25" s="4"/>
       <x:c r="X25" s="4"/>
@@ -6328,13 +6329,13 @@
       <x:c r="Z25" s="4"/>
       <x:c r="AA25" s="4"/>
       <x:c r="AB25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28">
       <x:c r="A26" s="4"/>
       <x:c r="B26" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C26" s="4"/>
       <x:c r="D26" s="4"/>
@@ -6344,27 +6345,27 @@
       <x:c r="H26" s="4"/>
       <x:c r="I26" s="4"/>
       <x:c r="J26" s="6" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="K26" s="4"/>
       <x:c r="L26" s="4"/>
       <x:c r="M26" s="6" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="N26" s="4"/>
       <x:c r="O26" s="4"/>
       <x:c r="P26" s="6" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="Q26" s="4"/>
       <x:c r="R26" s="4"/>
       <x:c r="S26" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T26" s="4"/>
       <x:c r="U26" s="4"/>
       <x:c r="V26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W26" s="4"/>
       <x:c r="X26" s="4"/>
@@ -6372,13 +6373,13 @@
       <x:c r="Z26" s="4"/>
       <x:c r="AA26" s="4"/>
       <x:c r="AB26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28">
       <x:c r="A27" s="4"/>
       <x:c r="B27" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
@@ -6388,27 +6389,27 @@
       <x:c r="H27" s="4"/>
       <x:c r="I27" s="4"/>
       <x:c r="J27" s="6" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="K27" s="4"/>
       <x:c r="L27" s="4"/>
       <x:c r="M27" s="6" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="N27" s="4"/>
       <x:c r="O27" s="4"/>
       <x:c r="P27" s="6" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="Q27" s="4"/>
       <x:c r="R27" s="4"/>
       <x:c r="S27" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T27" s="4"/>
       <x:c r="U27" s="4"/>
       <x:c r="V27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W27" s="4"/>
       <x:c r="X27" s="4"/>
@@ -6416,13 +6417,13 @@
       <x:c r="Z27" s="4"/>
       <x:c r="AA27" s="4"/>
       <x:c r="AB27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:28">
       <x:c r="A28" s="4"/>
       <x:c r="B28" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C28" s="4"/>
       <x:c r="D28" s="4"/>
@@ -6432,27 +6433,27 @@
       <x:c r="H28" s="4"/>
       <x:c r="I28" s="4"/>
       <x:c r="J28" s="6" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="K28" s="4"/>
       <x:c r="L28" s="4"/>
       <x:c r="M28" s="6" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="N28" s="4"/>
       <x:c r="O28" s="4"/>
       <x:c r="P28" s="6" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="Q28" s="4"/>
       <x:c r="R28" s="4"/>
       <x:c r="S28" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T28" s="4"/>
       <x:c r="U28" s="4"/>
       <x:c r="V28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W28" s="4"/>
       <x:c r="X28" s="4"/>
@@ -6460,13 +6461,13 @@
       <x:c r="Z28" s="4"/>
       <x:c r="AA28" s="4"/>
       <x:c r="AB28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28">
       <x:c r="A29" s="4"/>
       <x:c r="B29" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C29" s="4"/>
       <x:c r="D29" s="4"/>
@@ -6476,27 +6477,27 @@
       <x:c r="H29" s="4"/>
       <x:c r="I29" s="4"/>
       <x:c r="J29" s="6" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="K29" s="4"/>
       <x:c r="L29" s="4"/>
       <x:c r="M29" s="6" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="N29" s="4"/>
       <x:c r="O29" s="4"/>
       <x:c r="P29" s="6" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="Q29" s="4"/>
       <x:c r="R29" s="4"/>
       <x:c r="S29" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T29" s="4"/>
       <x:c r="U29" s="4"/>
       <x:c r="V29" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W29" s="4"/>
       <x:c r="X29" s="4"/>
@@ -6504,13 +6505,13 @@
       <x:c r="Z29" s="4"/>
       <x:c r="AA29" s="4"/>
       <x:c r="AB29" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28">
       <x:c r="A30" s="4"/>
       <x:c r="B30" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C30" s="4"/>
       <x:c r="D30" s="4"/>
@@ -6520,27 +6521,27 @@
       <x:c r="H30" s="4"/>
       <x:c r="I30" s="4"/>
       <x:c r="J30" s="6" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="K30" s="4"/>
       <x:c r="L30" s="4"/>
       <x:c r="M30" s="6" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="N30" s="4"/>
       <x:c r="O30" s="4"/>
       <x:c r="P30" s="6" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="Q30" s="4"/>
       <x:c r="R30" s="4"/>
       <x:c r="S30" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T30" s="4"/>
       <x:c r="U30" s="4"/>
       <x:c r="V30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="W30" s="4"/>
       <x:c r="X30" s="4"/>
@@ -6548,7 +6549,7 @@
       <x:c r="Z30" s="4"/>
       <x:c r="AA30" s="4"/>
       <x:c r="AB30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28">
@@ -6566,7 +6567,7 @@
       <x:c r="L31" s="4"/>
       <x:c r="M31" s="4"/>
       <x:c r="N31" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="O31" s="4"/>
       <x:c r="P31" s="4"/>
@@ -6593,27 +6594,27 @@
       <x:c r="G32" s="4"/>
       <x:c r="H32" s="4"/>
       <x:c r="I32" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J32" s="4"/>
       <x:c r="K32" s="4"/>
       <x:c r="L32" s="4"/>
       <x:c r="M32" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="N32" s="4"/>
       <x:c r="O32" s="4"/>
       <x:c r="P32" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="Q32" s="4"/>
       <x:c r="R32" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="S32" s="4"/>
       <x:c r="T32" s="4"/>
       <x:c r="U32" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="V32" s="4"/>
       <x:c r="W32" s="4"/>
@@ -6621,7 +6622,7 @@
       <x:c r="Y32" s="4"/>
       <x:c r="Z32" s="4"/>
       <x:c r="AA32" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AB32" s="4"/>
     </x:row>
@@ -6630,33 +6631,33 @@
       <x:c r="B33" s="4"/>
       <x:c r="C33" s="4"/>
       <x:c r="D33" s="5" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E33" s="4"/>
       <x:c r="F33" s="4"/>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="4"/>
       <x:c r="I33" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="J33" s="4"/>
       <x:c r="K33" s="4"/>
       <x:c r="L33" s="4"/>
       <x:c r="M33" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="N33" s="4"/>
       <x:c r="O33" s="4"/>
       <x:c r="P33" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="Q33" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="R33" s="4"/>
       <x:c r="S33" s="4"/>
       <x:c r="T33" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="U33" s="4"/>
       <x:c r="V33" s="4"/>
@@ -6664,7 +6665,7 @@
       <x:c r="X33" s="4"/>
       <x:c r="Y33" s="4"/>
       <x:c r="Z33" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AA33" s="4"/>
       <x:c r="AB33" s="4"/>
@@ -6683,19 +6684,19 @@
       <x:c r="K34" s="4"/>
       <x:c r="L34" s="4"/>
       <x:c r="M34" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N34" s="4"/>
       <x:c r="O34" s="4"/>
       <x:c r="P34" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="Q34" s="4"/>
       <x:c r="R34" s="4"/>
       <x:c r="S34" s="4"/>
       <x:c r="T34" s="4"/>
       <x:c r="U34" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="V34" s="4"/>
       <x:c r="W34" s="4"/>
@@ -6703,14 +6704,14 @@
       <x:c r="Y34" s="4"/>
       <x:c r="Z34" s="4"/>
       <x:c r="AA34" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AB34" s="4"/>
     </x:row>
     <x:row r="35" spans="1:28">
       <x:c r="A35" s="4"/>
       <x:c r="B35" s="5" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C35" s="4"/>
       <x:c r="D35" s="4"/>
@@ -6720,26 +6721,26 @@
       <x:c r="H35" s="4"/>
       <x:c r="I35" s="4"/>
       <x:c r="J35" s="6" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="K35" s="4"/>
       <x:c r="L35" s="4"/>
       <x:c r="M35" s="6" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="N35" s="4"/>
       <x:c r="O35" s="4"/>
       <x:c r="P35" s="6" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="Q35" s="4"/>
       <x:c r="R35" s="4"/>
       <x:c r="S35" s="6" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="T35" s="4"/>
       <x:c r="U35" s="6" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="V35" s="4"/>
       <x:c r="W35" s="4"/>
@@ -6747,14 +6748,14 @@
       <x:c r="Y35" s="4"/>
       <x:c r="Z35" s="4"/>
       <x:c r="AA35" s="6" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="AB35" s="4"/>
     </x:row>
     <x:row r="36" spans="1:28">
       <x:c r="A36" s="4"/>
       <x:c r="B36" s="5" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C36" s="4"/>
       <x:c r="D36" s="4"/>
@@ -6764,26 +6765,26 @@
       <x:c r="H36" s="4"/>
       <x:c r="I36" s="4"/>
       <x:c r="J36" s="6" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="K36" s="4"/>
       <x:c r="L36" s="4"/>
       <x:c r="M36" s="6" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="N36" s="4"/>
       <x:c r="O36" s="4"/>
       <x:c r="P36" s="6" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="Q36" s="4"/>
       <x:c r="R36" s="4"/>
       <x:c r="S36" s="6" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="T36" s="4"/>
       <x:c r="U36" s="6" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="V36" s="4"/>
       <x:c r="W36" s="4"/>
@@ -6791,14 +6792,14 @@
       <x:c r="Y36" s="4"/>
       <x:c r="Z36" s="4"/>
       <x:c r="AA36" s="6" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="AB36" s="4"/>
     </x:row>
     <x:row r="37" spans="1:28">
       <x:c r="A37" s="4"/>
       <x:c r="B37" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C37" s="4"/>
       <x:c r="D37" s="4"/>
@@ -6808,26 +6809,26 @@
       <x:c r="H37" s="4"/>
       <x:c r="I37" s="4"/>
       <x:c r="J37" s="6" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="K37" s="4"/>
       <x:c r="L37" s="4"/>
       <x:c r="M37" s="6" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="N37" s="4"/>
       <x:c r="O37" s="4"/>
       <x:c r="P37" s="6" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="Q37" s="4"/>
       <x:c r="R37" s="4"/>
       <x:c r="S37" s="6" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="T37" s="4"/>
       <x:c r="U37" s="6" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="V37" s="4"/>
       <x:c r="W37" s="4"/>
@@ -6835,14 +6836,14 @@
       <x:c r="Y37" s="4"/>
       <x:c r="Z37" s="4"/>
       <x:c r="AA37" s="6" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="AB37" s="4"/>
     </x:row>
     <x:row r="38" spans="1:28">
       <x:c r="A38" s="4"/>
       <x:c r="B38" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C38" s="4"/>
       <x:c r="D38" s="4"/>
@@ -6852,26 +6853,26 @@
       <x:c r="H38" s="4"/>
       <x:c r="I38" s="4"/>
       <x:c r="J38" s="6" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="K38" s="4"/>
       <x:c r="L38" s="4"/>
       <x:c r="M38" s="4"/>
       <x:c r="N38" s="6" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="O38" s="4"/>
       <x:c r="P38" s="6" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="Q38" s="4"/>
       <x:c r="R38" s="4"/>
       <x:c r="S38" s="6" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="T38" s="4"/>
       <x:c r="U38" s="6" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="V38" s="4"/>
       <x:c r="W38" s="4"/>
@@ -6879,14 +6880,14 @@
       <x:c r="Y38" s="4"/>
       <x:c r="Z38" s="4"/>
       <x:c r="AA38" s="6" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="AB38" s="4"/>
     </x:row>
     <x:row r="39" spans="1:28">
       <x:c r="A39" s="4"/>
       <x:c r="B39" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C39" s="4"/>
       <x:c r="D39" s="4"/>
@@ -6896,26 +6897,26 @@
       <x:c r="H39" s="4"/>
       <x:c r="I39" s="4"/>
       <x:c r="J39" s="6" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="K39" s="4"/>
       <x:c r="L39" s="4"/>
       <x:c r="M39" s="6" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="N39" s="4"/>
       <x:c r="O39" s="4"/>
       <x:c r="P39" s="6" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="Q39" s="4"/>
       <x:c r="R39" s="4"/>
       <x:c r="S39" s="6" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="T39" s="4"/>
       <x:c r="U39" s="6" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="V39" s="4"/>
       <x:c r="W39" s="4"/>
@@ -6923,14 +6924,14 @@
       <x:c r="Y39" s="4"/>
       <x:c r="Z39" s="4"/>
       <x:c r="AA39" s="6" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="AB39" s="4"/>
     </x:row>
     <x:row r="40" spans="1:28">
       <x:c r="A40" s="4"/>
       <x:c r="B40" s="5" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C40" s="4"/>
       <x:c r="D40" s="4"/>
@@ -6940,26 +6941,26 @@
       <x:c r="H40" s="4"/>
       <x:c r="I40" s="4"/>
       <x:c r="J40" s="6" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="K40" s="4"/>
       <x:c r="L40" s="4"/>
       <x:c r="M40" s="6" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="N40" s="4"/>
       <x:c r="O40" s="4"/>
       <x:c r="P40" s="6" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="Q40" s="4"/>
       <x:c r="R40" s="4"/>
       <x:c r="S40" s="6" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="T40" s="4"/>
       <x:c r="U40" s="6" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="V40" s="4"/>
       <x:c r="W40" s="4"/>
@@ -6967,25 +6968,25 @@
       <x:c r="Y40" s="4"/>
       <x:c r="Z40" s="4"/>
       <x:c r="AA40" s="6" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="AB40" s="4"/>
     </x:row>
     <x:row r="41" spans="1:28">
       <x:c r="A41" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B41" s="4"/>
       <x:c r="C41" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D41" s="4"/>
       <x:c r="E41" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="F41" s="4"/>
       <x:c r="G41" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H41" s="4"/>
       <x:c r="I41" s="4"/>
@@ -7006,13 +7007,13 @@
       <x:c r="X41" s="4"/>
       <x:c r="Y41" s="4"/>
       <x:c r="Z41" s="5" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="AA41" s="4"/>
       <x:c r="AB41" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1"/>
+  <x:sheetProtection password="8CAE" sheet="1" objects="1"/>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AB1"/>
     <x:mergeCell ref="A2:AB2"/>
@@ -7068,7 +7069,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:31" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -7103,7 +7104,7 @@
     </x:row>
     <x:row r="2" spans="1:31" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -7139,13 +7140,13 @@
     <x:row r="3" spans="1:31">
       <x:c r="A3" s="4"/>
       <x:c r="B3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
       <x:c r="E3" s="4"/>
       <x:c r="F3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G3" s="4"/>
       <x:c r="H3" s="4"/>
@@ -7158,7 +7159,7 @@
       <x:c r="O3" s="4"/>
       <x:c r="P3" s="4"/>
       <x:c r="Q3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R3" s="4"/>
       <x:c r="S3" s="4"/>
@@ -7169,7 +7170,7 @@
       <x:c r="X3" s="4"/>
       <x:c r="Y3" s="4"/>
       <x:c r="Z3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA3" s="4"/>
       <x:c r="AB3" s="4"/>
@@ -7180,7 +7181,7 @@
     <x:row r="4" spans="1:31">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -7189,7 +7190,7 @@
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
@@ -7199,7 +7200,7 @@
       <x:c r="O4" s="4"/>
       <x:c r="P4" s="4"/>
       <x:c r="Q4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="R4" s="4"/>
       <x:c r="S4" s="4"/>
@@ -7211,7 +7212,7 @@
       <x:c r="Y4" s="4"/>
       <x:c r="Z4" s="4"/>
       <x:c r="AA4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AB4" s="4"/>
       <x:c r="AC4" s="4"/>
@@ -7221,7 +7222,7 @@
     <x:row r="5" spans="1:31">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -7230,7 +7231,7 @@
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
@@ -7240,7 +7241,7 @@
       <x:c r="O5" s="4"/>
       <x:c r="P5" s="4"/>
       <x:c r="Q5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="R5" s="4"/>
       <x:c r="S5" s="4"/>
@@ -7251,7 +7252,7 @@
       <x:c r="X5" s="4"/>
       <x:c r="Y5" s="4"/>
       <x:c r="Z5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AA5" s="4"/>
       <x:c r="AB5" s="4"/>
@@ -7262,7 +7263,7 @@
     <x:row r="6" spans="1:31">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -7271,7 +7272,7 @@
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -7281,7 +7282,7 @@
       <x:c r="O6" s="4"/>
       <x:c r="P6" s="4"/>
       <x:c r="Q6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="R6" s="4"/>
       <x:c r="S6" s="4"/>
@@ -7294,7 +7295,7 @@
       <x:c r="Z6" s="4"/>
       <x:c r="AA6" s="4"/>
       <x:c r="AB6" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AC6" s="4"/>
       <x:c r="AD6" s="4"/>
@@ -7303,14 +7304,14 @@
     <x:row r="7" spans="1:31">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
@@ -7322,7 +7323,7 @@
       <x:c r="O7" s="4"/>
       <x:c r="P7" s="4"/>
       <x:c r="Q7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="R7" s="4"/>
       <x:c r="S7" s="4"/>
@@ -7335,7 +7336,7 @@
       <x:c r="Z7" s="4"/>
       <x:c r="AA7" s="4"/>
       <x:c r="AB7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AC7" s="4"/>
       <x:c r="AD7" s="4"/>
@@ -7344,12 +7345,12 @@
     <x:row r="8" spans="1:31">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
@@ -7373,7 +7374,7 @@
       <x:c r="Y8" s="4"/>
       <x:c r="Z8" s="4"/>
       <x:c r="AA8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AB8" s="4"/>
       <x:c r="AC8" s="4"/>
@@ -7391,7 +7392,7 @@
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="K9" s="4"/>
       <x:c r="L9" s="4"/>
@@ -7429,7 +7430,7 @@
       <x:c r="K10" s="4"/>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4"/>
@@ -7467,7 +7468,7 @@
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
@@ -7496,28 +7497,28 @@
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K12" s="4"/>
       <x:c r="L12" s="4"/>
       <x:c r="M12" s="4"/>
       <x:c r="N12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4"/>
       <x:c r="T12" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="U12" s="4"/>
       <x:c r="V12" s="4"/>
       <x:c r="W12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="X12" s="4"/>
       <x:c r="Y12" s="4"/>
@@ -7526,7 +7527,7 @@
       <x:c r="AB12" s="4"/>
       <x:c r="AC12" s="4"/>
       <x:c r="AD12" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AE12" s="4"/>
     </x:row>
@@ -7535,7 +7536,7 @@
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="5" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
@@ -7543,27 +7544,27 @@
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K13" s="4"/>
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
       <x:c r="N13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
       <x:c r="Q13" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="T13" s="4"/>
       <x:c r="U13" s="4"/>
       <x:c r="V13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="W13" s="4"/>
       <x:c r="X13" s="4"/>
@@ -7572,7 +7573,7 @@
       <x:c r="AA13" s="4"/>
       <x:c r="AB13" s="4"/>
       <x:c r="AC13" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AD13" s="4"/>
       <x:c r="AE13" s="4"/>
@@ -7592,12 +7593,12 @@
       <x:c r="L14" s="4"/>
       <x:c r="M14" s="4"/>
       <x:c r="N14" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="O14" s="4"/>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="4"/>
@@ -7605,7 +7606,7 @@
       <x:c r="U14" s="4"/>
       <x:c r="V14" s="4"/>
       <x:c r="W14" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="X14" s="4"/>
       <x:c r="Y14" s="4"/>
@@ -7614,14 +7615,14 @@
       <x:c r="AB14" s="4"/>
       <x:c r="AC14" s="4"/>
       <x:c r="AD14" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AE14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:31">
       <x:c r="A15" s="4"/>
       <x:c r="B15" s="5" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -7632,29 +7633,29 @@
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
       <x:c r="K15" s="6" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
       <x:c r="N15" s="6" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="6" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="4"/>
       <x:c r="T15" s="4"/>
       <x:c r="U15" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V15" s="4"/>
       <x:c r="W15" s="4"/>
       <x:c r="X15" s="4"/>
       <x:c r="Y15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z15" s="4"/>
       <x:c r="AA15" s="4"/>
@@ -7662,13 +7663,13 @@
       <x:c r="AC15" s="4"/>
       <x:c r="AD15" s="4"/>
       <x:c r="AE15" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:31">
       <x:c r="A16" s="4"/>
       <x:c r="B16" s="5" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
@@ -7679,29 +7680,29 @@
       <x:c r="I16" s="4"/>
       <x:c r="J16" s="4"/>
       <x:c r="K16" s="6" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="L16" s="4"/>
       <x:c r="M16" s="4"/>
       <x:c r="N16" s="6" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
       <x:c r="Q16" s="6" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="4"/>
       <x:c r="T16" s="4"/>
       <x:c r="U16" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V16" s="4"/>
       <x:c r="W16" s="4"/>
       <x:c r="X16" s="4"/>
       <x:c r="Y16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z16" s="4"/>
       <x:c r="AA16" s="4"/>
@@ -7709,13 +7710,13 @@
       <x:c r="AC16" s="4"/>
       <x:c r="AD16" s="4"/>
       <x:c r="AE16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:31">
       <x:c r="A17" s="4"/>
       <x:c r="B17" s="5" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="4"/>
@@ -7726,29 +7727,29 @@
       <x:c r="I17" s="4"/>
       <x:c r="J17" s="4"/>
       <x:c r="K17" s="6" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="L17" s="4"/>
       <x:c r="M17" s="4"/>
       <x:c r="N17" s="6" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
       <x:c r="Q17" s="6" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="R17" s="4"/>
       <x:c r="S17" s="4"/>
       <x:c r="T17" s="4"/>
       <x:c r="U17" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V17" s="4"/>
       <x:c r="W17" s="4"/>
       <x:c r="X17" s="4"/>
       <x:c r="Y17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z17" s="4"/>
       <x:c r="AA17" s="4"/>
@@ -7756,13 +7757,13 @@
       <x:c r="AC17" s="4"/>
       <x:c r="AD17" s="4"/>
       <x:c r="AE17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:31">
       <x:c r="A18" s="4"/>
       <x:c r="B18" s="5" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="4"/>
@@ -7773,29 +7774,29 @@
       <x:c r="I18" s="4"/>
       <x:c r="J18" s="4"/>
       <x:c r="K18" s="6" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="L18" s="4"/>
       <x:c r="M18" s="4"/>
       <x:c r="N18" s="6" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="O18" s="4"/>
       <x:c r="P18" s="4"/>
       <x:c r="Q18" s="6" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="R18" s="4"/>
       <x:c r="S18" s="4"/>
       <x:c r="T18" s="4"/>
       <x:c r="U18" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V18" s="4"/>
       <x:c r="W18" s="4"/>
       <x:c r="X18" s="4"/>
       <x:c r="Y18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z18" s="4"/>
       <x:c r="AA18" s="4"/>
@@ -7803,13 +7804,13 @@
       <x:c r="AC18" s="4"/>
       <x:c r="AD18" s="4"/>
       <x:c r="AE18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:31">
       <x:c r="A19" s="4"/>
       <x:c r="B19" s="5" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C19" s="4"/>
       <x:c r="D19" s="4"/>
@@ -7820,29 +7821,29 @@
       <x:c r="I19" s="4"/>
       <x:c r="J19" s="4"/>
       <x:c r="K19" s="6" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="L19" s="4"/>
       <x:c r="M19" s="4"/>
       <x:c r="N19" s="6" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="O19" s="4"/>
       <x:c r="P19" s="4"/>
       <x:c r="Q19" s="6" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="R19" s="4"/>
       <x:c r="S19" s="4"/>
       <x:c r="T19" s="4"/>
       <x:c r="U19" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V19" s="4"/>
       <x:c r="W19" s="4"/>
       <x:c r="X19" s="4"/>
       <x:c r="Y19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z19" s="4"/>
       <x:c r="AA19" s="4"/>
@@ -7850,13 +7851,13 @@
       <x:c r="AC19" s="4"/>
       <x:c r="AD19" s="4"/>
       <x:c r="AE19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:31">
       <x:c r="A20" s="4"/>
       <x:c r="B20" s="5" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C20" s="4"/>
       <x:c r="D20" s="4"/>
@@ -7867,29 +7868,29 @@
       <x:c r="I20" s="4"/>
       <x:c r="J20" s="4"/>
       <x:c r="K20" s="6" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="4"/>
       <x:c r="N20" s="6" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="O20" s="4"/>
       <x:c r="P20" s="4"/>
       <x:c r="Q20" s="6" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="R20" s="4"/>
       <x:c r="S20" s="4"/>
       <x:c r="T20" s="4"/>
       <x:c r="U20" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V20" s="4"/>
       <x:c r="W20" s="4"/>
       <x:c r="X20" s="4"/>
       <x:c r="Y20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z20" s="4"/>
       <x:c r="AA20" s="4"/>
@@ -7897,13 +7898,13 @@
       <x:c r="AC20" s="4"/>
       <x:c r="AD20" s="4"/>
       <x:c r="AE20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:31">
       <x:c r="A21" s="4"/>
       <x:c r="B21" s="5" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C21" s="4"/>
       <x:c r="D21" s="4"/>
@@ -7914,29 +7915,29 @@
       <x:c r="I21" s="4"/>
       <x:c r="J21" s="4"/>
       <x:c r="K21" s="6" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="L21" s="4"/>
       <x:c r="M21" s="4"/>
       <x:c r="N21" s="6" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="O21" s="4"/>
       <x:c r="P21" s="4"/>
       <x:c r="Q21" s="6" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="R21" s="4"/>
       <x:c r="S21" s="4"/>
       <x:c r="T21" s="4"/>
       <x:c r="U21" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V21" s="4"/>
       <x:c r="W21" s="4"/>
       <x:c r="X21" s="4"/>
       <x:c r="Y21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z21" s="4"/>
       <x:c r="AA21" s="4"/>
@@ -7944,13 +7945,13 @@
       <x:c r="AC21" s="4"/>
       <x:c r="AD21" s="4"/>
       <x:c r="AE21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:31">
       <x:c r="A22" s="4"/>
       <x:c r="B22" s="5" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C22" s="4"/>
       <x:c r="D22" s="4"/>
@@ -7961,29 +7962,29 @@
       <x:c r="I22" s="4"/>
       <x:c r="J22" s="4"/>
       <x:c r="K22" s="6" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="L22" s="4"/>
       <x:c r="M22" s="4"/>
       <x:c r="N22" s="6" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="O22" s="4"/>
       <x:c r="P22" s="4"/>
       <x:c r="Q22" s="6" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="R22" s="4"/>
       <x:c r="S22" s="4"/>
       <x:c r="T22" s="4"/>
       <x:c r="U22" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V22" s="4"/>
       <x:c r="W22" s="4"/>
       <x:c r="X22" s="4"/>
       <x:c r="Y22" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z22" s="4"/>
       <x:c r="AA22" s="4"/>
@@ -7991,13 +7992,13 @@
       <x:c r="AC22" s="4"/>
       <x:c r="AD22" s="4"/>
       <x:c r="AE22" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:31">
       <x:c r="A23" s="4"/>
       <x:c r="B23" s="5" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C23" s="4"/>
       <x:c r="D23" s="4"/>
@@ -8008,29 +8009,29 @@
       <x:c r="I23" s="4"/>
       <x:c r="J23" s="4"/>
       <x:c r="K23" s="6" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="L23" s="4"/>
       <x:c r="M23" s="4"/>
       <x:c r="N23" s="6" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="O23" s="4"/>
       <x:c r="P23" s="4"/>
       <x:c r="Q23" s="6" t="s">
-        <x:v>339</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="R23" s="4"/>
       <x:c r="S23" s="4"/>
       <x:c r="T23" s="4"/>
       <x:c r="U23" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V23" s="4"/>
       <x:c r="W23" s="4"/>
       <x:c r="X23" s="4"/>
       <x:c r="Y23" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z23" s="4"/>
       <x:c r="AA23" s="4"/>
@@ -8038,13 +8039,13 @@
       <x:c r="AC23" s="4"/>
       <x:c r="AD23" s="4"/>
       <x:c r="AE23" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:31">
       <x:c r="A24" s="4"/>
       <x:c r="B24" s="5" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C24" s="4"/>
       <x:c r="D24" s="4"/>
@@ -8055,29 +8056,29 @@
       <x:c r="I24" s="4"/>
       <x:c r="J24" s="4"/>
       <x:c r="K24" s="6" t="s">
-        <x:v>341</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="L24" s="4"/>
       <x:c r="M24" s="4"/>
       <x:c r="N24" s="6" t="s">
-        <x:v>342</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="O24" s="4"/>
       <x:c r="P24" s="4"/>
       <x:c r="Q24" s="6" t="s">
-        <x:v>343</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="R24" s="4"/>
       <x:c r="S24" s="4"/>
       <x:c r="T24" s="4"/>
       <x:c r="U24" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V24" s="4"/>
       <x:c r="W24" s="4"/>
       <x:c r="X24" s="4"/>
       <x:c r="Y24" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z24" s="4"/>
       <x:c r="AA24" s="4"/>
@@ -8085,13 +8086,13 @@
       <x:c r="AC24" s="4"/>
       <x:c r="AD24" s="4"/>
       <x:c r="AE24" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:31">
       <x:c r="A25" s="4"/>
       <x:c r="B25" s="5" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C25" s="4"/>
       <x:c r="D25" s="4"/>
@@ -8102,29 +8103,29 @@
       <x:c r="I25" s="4"/>
       <x:c r="J25" s="4"/>
       <x:c r="K25" s="6" t="s">
-        <x:v>345</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="L25" s="4"/>
       <x:c r="M25" s="4"/>
       <x:c r="N25" s="6" t="s">
-        <x:v>346</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="O25" s="4"/>
       <x:c r="P25" s="4"/>
       <x:c r="Q25" s="6" t="s">
-        <x:v>347</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="R25" s="4"/>
       <x:c r="S25" s="4"/>
       <x:c r="T25" s="4"/>
       <x:c r="U25" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V25" s="4"/>
       <x:c r="W25" s="4"/>
       <x:c r="X25" s="4"/>
       <x:c r="Y25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z25" s="4"/>
       <x:c r="AA25" s="4"/>
@@ -8132,13 +8133,13 @@
       <x:c r="AC25" s="4"/>
       <x:c r="AD25" s="4"/>
       <x:c r="AE25" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:31">
       <x:c r="A26" s="4"/>
       <x:c r="B26" s="5" t="s">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C26" s="4"/>
       <x:c r="D26" s="4"/>
@@ -8149,29 +8150,29 @@
       <x:c r="I26" s="4"/>
       <x:c r="J26" s="4"/>
       <x:c r="K26" s="6" t="s">
-        <x:v>349</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="L26" s="4"/>
       <x:c r="M26" s="4"/>
       <x:c r="N26" s="6" t="s">
-        <x:v>350</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="O26" s="4"/>
       <x:c r="P26" s="4"/>
       <x:c r="Q26" s="6" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="R26" s="4"/>
       <x:c r="S26" s="4"/>
       <x:c r="T26" s="4"/>
       <x:c r="U26" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V26" s="4"/>
       <x:c r="W26" s="4"/>
       <x:c r="X26" s="4"/>
       <x:c r="Y26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z26" s="4"/>
       <x:c r="AA26" s="4"/>
@@ -8179,13 +8180,13 @@
       <x:c r="AC26" s="4"/>
       <x:c r="AD26" s="4"/>
       <x:c r="AE26" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:31">
       <x:c r="A27" s="4"/>
       <x:c r="B27" s="5" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
@@ -8196,29 +8197,29 @@
       <x:c r="I27" s="4"/>
       <x:c r="J27" s="4"/>
       <x:c r="K27" s="6" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="L27" s="4"/>
       <x:c r="M27" s="4"/>
       <x:c r="N27" s="6" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="O27" s="4"/>
       <x:c r="P27" s="4"/>
       <x:c r="Q27" s="6" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="R27" s="4"/>
       <x:c r="S27" s="4"/>
       <x:c r="T27" s="4"/>
       <x:c r="U27" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V27" s="4"/>
       <x:c r="W27" s="4"/>
       <x:c r="X27" s="4"/>
       <x:c r="Y27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z27" s="4"/>
       <x:c r="AA27" s="4"/>
@@ -8226,13 +8227,13 @@
       <x:c r="AC27" s="4"/>
       <x:c r="AD27" s="4"/>
       <x:c r="AE27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:31">
       <x:c r="A28" s="4"/>
       <x:c r="B28" s="5" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C28" s="4"/>
       <x:c r="D28" s="4"/>
@@ -8243,29 +8244,29 @@
       <x:c r="I28" s="4"/>
       <x:c r="J28" s="4"/>
       <x:c r="K28" s="6" t="s">
-        <x:v>357</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="L28" s="4"/>
       <x:c r="M28" s="4"/>
       <x:c r="N28" s="6" t="s">
-        <x:v>358</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="O28" s="4"/>
       <x:c r="P28" s="4"/>
       <x:c r="Q28" s="6" t="s">
-        <x:v>359</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="R28" s="4"/>
       <x:c r="S28" s="4"/>
       <x:c r="T28" s="4"/>
       <x:c r="U28" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V28" s="4"/>
       <x:c r="W28" s="4"/>
       <x:c r="X28" s="4"/>
       <x:c r="Y28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z28" s="4"/>
       <x:c r="AA28" s="4"/>
@@ -8273,13 +8274,13 @@
       <x:c r="AC28" s="4"/>
       <x:c r="AD28" s="4"/>
       <x:c r="AE28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:31">
       <x:c r="A29" s="4"/>
       <x:c r="B29" s="5" t="s">
-        <x:v>360</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C29" s="4"/>
       <x:c r="D29" s="4"/>
@@ -8290,29 +8291,29 @@
       <x:c r="I29" s="4"/>
       <x:c r="J29" s="4"/>
       <x:c r="K29" s="6" t="s">
-        <x:v>361</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="L29" s="4"/>
       <x:c r="M29" s="4"/>
       <x:c r="N29" s="6" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="O29" s="4"/>
       <x:c r="P29" s="4"/>
       <x:c r="Q29" s="6" t="s">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="R29" s="4"/>
       <x:c r="S29" s="4"/>
       <x:c r="T29" s="4"/>
       <x:c r="U29" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V29" s="4"/>
       <x:c r="W29" s="4"/>
       <x:c r="X29" s="4"/>
       <x:c r="Y29" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z29" s="4"/>
       <x:c r="AA29" s="4"/>
@@ -8320,13 +8321,13 @@
       <x:c r="AC29" s="4"/>
       <x:c r="AD29" s="4"/>
       <x:c r="AE29" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:31">
       <x:c r="A30" s="4"/>
       <x:c r="B30" s="5" t="s">
-        <x:v>364</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C30" s="4"/>
       <x:c r="D30" s="4"/>
@@ -8337,29 +8338,29 @@
       <x:c r="I30" s="4"/>
       <x:c r="J30" s="4"/>
       <x:c r="K30" s="6" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="L30" s="4"/>
       <x:c r="M30" s="4"/>
       <x:c r="N30" s="6" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="O30" s="4"/>
       <x:c r="P30" s="4"/>
       <x:c r="Q30" s="6" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="R30" s="4"/>
       <x:c r="S30" s="4"/>
       <x:c r="T30" s="4"/>
       <x:c r="U30" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V30" s="4"/>
       <x:c r="W30" s="4"/>
       <x:c r="X30" s="4"/>
       <x:c r="Y30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z30" s="4"/>
       <x:c r="AA30" s="4"/>
@@ -8367,13 +8368,13 @@
       <x:c r="AC30" s="4"/>
       <x:c r="AD30" s="4"/>
       <x:c r="AE30" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:31">
       <x:c r="A31" s="4"/>
       <x:c r="B31" s="5" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C31" s="4"/>
       <x:c r="D31" s="4"/>
@@ -8384,29 +8385,29 @@
       <x:c r="I31" s="4"/>
       <x:c r="J31" s="4"/>
       <x:c r="K31" s="6" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="L31" s="4"/>
       <x:c r="M31" s="4"/>
       <x:c r="N31" s="6" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="O31" s="4"/>
       <x:c r="P31" s="4"/>
       <x:c r="Q31" s="6" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="R31" s="4"/>
       <x:c r="S31" s="4"/>
       <x:c r="T31" s="4"/>
       <x:c r="U31" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V31" s="4"/>
       <x:c r="W31" s="4"/>
       <x:c r="X31" s="4"/>
       <x:c r="Y31" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z31" s="4"/>
       <x:c r="AA31" s="4"/>
@@ -8414,13 +8415,13 @@
       <x:c r="AC31" s="4"/>
       <x:c r="AD31" s="4"/>
       <x:c r="AE31" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:31">
       <x:c r="A32" s="4"/>
       <x:c r="B32" s="5" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C32" s="4"/>
       <x:c r="D32" s="4"/>
@@ -8431,29 +8432,29 @@
       <x:c r="I32" s="4"/>
       <x:c r="J32" s="4"/>
       <x:c r="K32" s="6" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="L32" s="4"/>
       <x:c r="M32" s="4"/>
       <x:c r="N32" s="6" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="O32" s="4"/>
       <x:c r="P32" s="4"/>
       <x:c r="Q32" s="6" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="R32" s="4"/>
       <x:c r="S32" s="4"/>
       <x:c r="T32" s="4"/>
       <x:c r="U32" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V32" s="4"/>
       <x:c r="W32" s="4"/>
       <x:c r="X32" s="4"/>
       <x:c r="Y32" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z32" s="4"/>
       <x:c r="AA32" s="4"/>
@@ -8461,13 +8462,13 @@
       <x:c r="AC32" s="4"/>
       <x:c r="AD32" s="4"/>
       <x:c r="AE32" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:31">
       <x:c r="A33" s="4"/>
       <x:c r="B33" s="5" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C33" s="4"/>
       <x:c r="D33" s="4"/>
@@ -8478,29 +8479,29 @@
       <x:c r="I33" s="4"/>
       <x:c r="J33" s="4"/>
       <x:c r="K33" s="6" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="L33" s="4"/>
       <x:c r="M33" s="4"/>
       <x:c r="N33" s="6" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="O33" s="4"/>
       <x:c r="P33" s="4"/>
       <x:c r="Q33" s="6" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="R33" s="4"/>
       <x:c r="S33" s="4"/>
       <x:c r="T33" s="4"/>
       <x:c r="U33" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V33" s="4"/>
       <x:c r="W33" s="4"/>
       <x:c r="X33" s="4"/>
       <x:c r="Y33" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z33" s="4"/>
       <x:c r="AA33" s="4"/>
@@ -8508,13 +8509,13 @@
       <x:c r="AC33" s="4"/>
       <x:c r="AD33" s="4"/>
       <x:c r="AE33" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:31">
       <x:c r="A34" s="4"/>
       <x:c r="B34" s="5" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C34" s="4"/>
       <x:c r="D34" s="4"/>
@@ -8525,29 +8526,29 @@
       <x:c r="I34" s="4"/>
       <x:c r="J34" s="4"/>
       <x:c r="K34" s="6" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="L34" s="4"/>
       <x:c r="M34" s="4"/>
       <x:c r="N34" s="4"/>
       <x:c r="O34" s="6" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="P34" s="4"/>
       <x:c r="Q34" s="4"/>
       <x:c r="R34" s="6" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="S34" s="4"/>
       <x:c r="T34" s="4"/>
       <x:c r="U34" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V34" s="4"/>
       <x:c r="W34" s="4"/>
       <x:c r="X34" s="4"/>
       <x:c r="Y34" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z34" s="4"/>
       <x:c r="AA34" s="4"/>
@@ -8555,7 +8556,7 @@
       <x:c r="AC34" s="4"/>
       <x:c r="AD34" s="4"/>
       <x:c r="AE34" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:31">
@@ -8574,7 +8575,7 @@
       <x:c r="M35" s="4"/>
       <x:c r="N35" s="4"/>
       <x:c r="O35" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="P35" s="4"/>
       <x:c r="Q35" s="4"/>
@@ -8604,28 +8605,28 @@
       <x:c r="H36" s="4"/>
       <x:c r="I36" s="4"/>
       <x:c r="J36" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K36" s="4"/>
       <x:c r="L36" s="4"/>
       <x:c r="M36" s="4"/>
       <x:c r="N36" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="O36" s="4"/>
       <x:c r="P36" s="4"/>
       <x:c r="Q36" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="R36" s="4"/>
       <x:c r="S36" s="4"/>
       <x:c r="T36" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="U36" s="4"/>
       <x:c r="V36" s="4"/>
       <x:c r="W36" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="X36" s="4"/>
       <x:c r="Y36" s="4"/>
@@ -8634,7 +8635,7 @@
       <x:c r="AB36" s="4"/>
       <x:c r="AC36" s="4"/>
       <x:c r="AD36" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AE36" s="4"/>
     </x:row>
@@ -8644,34 +8645,34 @@
       <x:c r="C37" s="4"/>
       <x:c r="D37" s="4"/>
       <x:c r="E37" s="5" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F37" s="4"/>
       <x:c r="G37" s="4"/>
       <x:c r="H37" s="4"/>
       <x:c r="I37" s="4"/>
       <x:c r="J37" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K37" s="4"/>
       <x:c r="L37" s="4"/>
       <x:c r="M37" s="4"/>
       <x:c r="N37" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="O37" s="4"/>
       <x:c r="P37" s="4"/>
       <x:c r="Q37" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="R37" s="4"/>
       <x:c r="S37" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="T37" s="4"/>
       <x:c r="U37" s="4"/>
       <x:c r="V37" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="W37" s="4"/>
       <x:c r="X37" s="4"/>
@@ -8680,7 +8681,7 @@
       <x:c r="AA37" s="4"/>
       <x:c r="AB37" s="4"/>
       <x:c r="AC37" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AD37" s="4"/>
       <x:c r="AE37" s="4"/>
@@ -8700,12 +8701,12 @@
       <x:c r="L38" s="4"/>
       <x:c r="M38" s="4"/>
       <x:c r="N38" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="O38" s="4"/>
       <x:c r="P38" s="4"/>
       <x:c r="Q38" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R38" s="4"/>
       <x:c r="S38" s="4"/>
@@ -8713,7 +8714,7 @@
       <x:c r="U38" s="4"/>
       <x:c r="V38" s="4"/>
       <x:c r="W38" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="X38" s="4"/>
       <x:c r="Y38" s="4"/>
@@ -8722,14 +8723,14 @@
       <x:c r="AB38" s="4"/>
       <x:c r="AC38" s="4"/>
       <x:c r="AD38" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AE38" s="4"/>
     </x:row>
     <x:row r="39" spans="1:31">
       <x:c r="A39" s="4"/>
       <x:c r="B39" s="5" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C39" s="4"/>
       <x:c r="D39" s="4"/>
@@ -8740,29 +8741,29 @@
       <x:c r="I39" s="4"/>
       <x:c r="J39" s="4"/>
       <x:c r="K39" s="6" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="L39" s="4"/>
       <x:c r="M39" s="4"/>
       <x:c r="N39" s="6" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="O39" s="4"/>
       <x:c r="P39" s="4"/>
       <x:c r="Q39" s="6" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="R39" s="4"/>
       <x:c r="S39" s="4"/>
       <x:c r="T39" s="4"/>
       <x:c r="U39" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V39" s="4"/>
       <x:c r="W39" s="4"/>
       <x:c r="X39" s="4"/>
       <x:c r="Y39" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z39" s="4"/>
       <x:c r="AA39" s="4"/>
@@ -8770,13 +8771,13 @@
       <x:c r="AC39" s="4"/>
       <x:c r="AD39" s="4"/>
       <x:c r="AE39" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:31">
       <x:c r="A40" s="4"/>
       <x:c r="B40" s="5" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C40" s="4"/>
       <x:c r="D40" s="4"/>
@@ -8787,29 +8788,29 @@
       <x:c r="I40" s="4"/>
       <x:c r="J40" s="4"/>
       <x:c r="K40" s="6" t="s">
-        <x:v>386</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="L40" s="4"/>
       <x:c r="M40" s="4"/>
       <x:c r="N40" s="6" t="s">
-        <x:v>387</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="O40" s="4"/>
       <x:c r="P40" s="4"/>
       <x:c r="Q40" s="6" t="s">
-        <x:v>388</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="R40" s="4"/>
       <x:c r="S40" s="4"/>
       <x:c r="T40" s="4"/>
       <x:c r="U40" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V40" s="4"/>
       <x:c r="W40" s="4"/>
       <x:c r="X40" s="4"/>
       <x:c r="Y40" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z40" s="4"/>
       <x:c r="AA40" s="4"/>
@@ -8817,13 +8818,13 @@
       <x:c r="AC40" s="4"/>
       <x:c r="AD40" s="4"/>
       <x:c r="AE40" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:31">
       <x:c r="A41" s="4"/>
       <x:c r="B41" s="5" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C41" s="4"/>
       <x:c r="D41" s="4"/>
@@ -8834,29 +8835,29 @@
       <x:c r="I41" s="4"/>
       <x:c r="J41" s="4"/>
       <x:c r="K41" s="6" t="s">
-        <x:v>389</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="L41" s="4"/>
       <x:c r="M41" s="4"/>
       <x:c r="N41" s="6" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="O41" s="4"/>
       <x:c r="P41" s="4"/>
       <x:c r="Q41" s="6" t="s">
-        <x:v>391</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="R41" s="4"/>
       <x:c r="S41" s="4"/>
       <x:c r="T41" s="4"/>
       <x:c r="U41" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V41" s="4"/>
       <x:c r="W41" s="4"/>
       <x:c r="X41" s="4"/>
       <x:c r="Y41" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z41" s="4"/>
       <x:c r="AA41" s="4"/>
@@ -8864,13 +8865,13 @@
       <x:c r="AC41" s="4"/>
       <x:c r="AD41" s="4"/>
       <x:c r="AE41" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:31">
       <x:c r="A42" s="4"/>
       <x:c r="B42" s="5" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C42" s="4"/>
       <x:c r="D42" s="4"/>
@@ -8881,29 +8882,29 @@
       <x:c r="I42" s="4"/>
       <x:c r="J42" s="4"/>
       <x:c r="K42" s="6" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="L42" s="4"/>
       <x:c r="M42" s="4"/>
       <x:c r="N42" s="6" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="O42" s="4"/>
       <x:c r="P42" s="4"/>
       <x:c r="Q42" s="6" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="R42" s="4"/>
       <x:c r="S42" s="4"/>
       <x:c r="T42" s="4"/>
       <x:c r="U42" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V42" s="4"/>
       <x:c r="W42" s="4"/>
       <x:c r="X42" s="4"/>
       <x:c r="Y42" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z42" s="4"/>
       <x:c r="AA42" s="4"/>
@@ -8911,13 +8912,13 @@
       <x:c r="AC42" s="4"/>
       <x:c r="AD42" s="4"/>
       <x:c r="AE42" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:31">
       <x:c r="A43" s="4"/>
       <x:c r="B43" s="5" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C43" s="4"/>
       <x:c r="D43" s="4"/>
@@ -8928,29 +8929,29 @@
       <x:c r="I43" s="4"/>
       <x:c r="J43" s="4"/>
       <x:c r="K43" s="6" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="L43" s="4"/>
       <x:c r="M43" s="4"/>
       <x:c r="N43" s="6" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="O43" s="4"/>
       <x:c r="P43" s="4"/>
       <x:c r="Q43" s="6" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="R43" s="4"/>
       <x:c r="S43" s="4"/>
       <x:c r="T43" s="4"/>
       <x:c r="U43" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V43" s="4"/>
       <x:c r="W43" s="4"/>
       <x:c r="X43" s="4"/>
       <x:c r="Y43" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z43" s="4"/>
       <x:c r="AA43" s="4"/>
@@ -8958,13 +8959,13 @@
       <x:c r="AC43" s="4"/>
       <x:c r="AD43" s="4"/>
       <x:c r="AE43" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:31">
       <x:c r="A44" s="4"/>
       <x:c r="B44" s="5" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C44" s="4"/>
       <x:c r="D44" s="4"/>
@@ -8975,29 +8976,29 @@
       <x:c r="I44" s="4"/>
       <x:c r="J44" s="4"/>
       <x:c r="K44" s="6" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="L44" s="4"/>
       <x:c r="M44" s="4"/>
       <x:c r="N44" s="6" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="O44" s="4"/>
       <x:c r="P44" s="4"/>
       <x:c r="Q44" s="6" t="s">
-        <x:v>400</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="R44" s="4"/>
       <x:c r="S44" s="4"/>
       <x:c r="T44" s="4"/>
       <x:c r="U44" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V44" s="4"/>
       <x:c r="W44" s="4"/>
       <x:c r="X44" s="4"/>
       <x:c r="Y44" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z44" s="4"/>
       <x:c r="AA44" s="4"/>
@@ -9005,13 +9006,13 @@
       <x:c r="AC44" s="4"/>
       <x:c r="AD44" s="4"/>
       <x:c r="AE44" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:31">
       <x:c r="A45" s="4"/>
       <x:c r="B45" s="5" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C45" s="4"/>
       <x:c r="D45" s="4"/>
@@ -9022,29 +9023,29 @@
       <x:c r="I45" s="4"/>
       <x:c r="J45" s="4"/>
       <x:c r="K45" s="6" t="s">
-        <x:v>401</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="L45" s="4"/>
       <x:c r="M45" s="4"/>
       <x:c r="N45" s="6" t="s">
-        <x:v>402</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="O45" s="4"/>
       <x:c r="P45" s="4"/>
       <x:c r="Q45" s="6" t="s">
-        <x:v>403</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="R45" s="4"/>
       <x:c r="S45" s="4"/>
       <x:c r="T45" s="4"/>
       <x:c r="U45" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V45" s="4"/>
       <x:c r="W45" s="4"/>
       <x:c r="X45" s="4"/>
       <x:c r="Y45" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z45" s="4"/>
       <x:c r="AA45" s="4"/>
@@ -9052,13 +9053,13 @@
       <x:c r="AC45" s="4"/>
       <x:c r="AD45" s="4"/>
       <x:c r="AE45" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:31">
       <x:c r="A46" s="4"/>
       <x:c r="B46" s="5" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C46" s="4"/>
       <x:c r="D46" s="4"/>
@@ -9069,29 +9070,29 @@
       <x:c r="I46" s="4"/>
       <x:c r="J46" s="4"/>
       <x:c r="K46" s="6" t="s">
-        <x:v>404</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="L46" s="4"/>
       <x:c r="M46" s="4"/>
       <x:c r="N46" s="6" t="s">
-        <x:v>405</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="O46" s="4"/>
       <x:c r="P46" s="4"/>
       <x:c r="Q46" s="6" t="s">
-        <x:v>406</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="R46" s="4"/>
       <x:c r="S46" s="4"/>
       <x:c r="T46" s="4"/>
       <x:c r="U46" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V46" s="4"/>
       <x:c r="W46" s="4"/>
       <x:c r="X46" s="4"/>
       <x:c r="Y46" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z46" s="4"/>
       <x:c r="AA46" s="4"/>
@@ -9099,13 +9100,13 @@
       <x:c r="AC46" s="4"/>
       <x:c r="AD46" s="4"/>
       <x:c r="AE46" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:31">
       <x:c r="A47" s="4"/>
       <x:c r="B47" s="5" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C47" s="4"/>
       <x:c r="D47" s="4"/>
@@ -9116,29 +9117,29 @@
       <x:c r="I47" s="4"/>
       <x:c r="J47" s="4"/>
       <x:c r="K47" s="6" t="s">
-        <x:v>407</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="L47" s="4"/>
       <x:c r="M47" s="4"/>
       <x:c r="N47" s="6" t="s">
-        <x:v>408</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="O47" s="4"/>
       <x:c r="P47" s="4"/>
       <x:c r="Q47" s="6" t="s">
-        <x:v>409</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="R47" s="4"/>
       <x:c r="S47" s="4"/>
       <x:c r="T47" s="4"/>
       <x:c r="U47" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V47" s="4"/>
       <x:c r="W47" s="4"/>
       <x:c r="X47" s="4"/>
       <x:c r="Y47" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z47" s="4"/>
       <x:c r="AA47" s="4"/>
@@ -9146,13 +9147,13 @@
       <x:c r="AC47" s="4"/>
       <x:c r="AD47" s="4"/>
       <x:c r="AE47" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:31">
       <x:c r="A48" s="4"/>
       <x:c r="B48" s="5" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C48" s="4"/>
       <x:c r="D48" s="4"/>
@@ -9163,29 +9164,29 @@
       <x:c r="I48" s="4"/>
       <x:c r="J48" s="4"/>
       <x:c r="K48" s="6" t="s">
-        <x:v>410</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="L48" s="4"/>
       <x:c r="M48" s="4"/>
       <x:c r="N48" s="6" t="s">
-        <x:v>411</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="O48" s="4"/>
       <x:c r="P48" s="4"/>
       <x:c r="Q48" s="6" t="s">
-        <x:v>412</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="R48" s="4"/>
       <x:c r="S48" s="4"/>
       <x:c r="T48" s="4"/>
       <x:c r="U48" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V48" s="4"/>
       <x:c r="W48" s="4"/>
       <x:c r="X48" s="4"/>
       <x:c r="Y48" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z48" s="4"/>
       <x:c r="AA48" s="4"/>
@@ -9193,13 +9194,13 @@
       <x:c r="AC48" s="4"/>
       <x:c r="AD48" s="4"/>
       <x:c r="AE48" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:31">
       <x:c r="A49" s="4"/>
       <x:c r="B49" s="5" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C49" s="4"/>
       <x:c r="D49" s="4"/>
@@ -9210,29 +9211,29 @@
       <x:c r="I49" s="4"/>
       <x:c r="J49" s="4"/>
       <x:c r="K49" s="6" t="s">
-        <x:v>413</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="L49" s="4"/>
       <x:c r="M49" s="4"/>
       <x:c r="N49" s="6" t="s">
-        <x:v>414</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="O49" s="4"/>
       <x:c r="P49" s="4"/>
       <x:c r="Q49" s="6" t="s">
-        <x:v>415</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="R49" s="4"/>
       <x:c r="S49" s="4"/>
       <x:c r="T49" s="4"/>
       <x:c r="U49" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V49" s="4"/>
       <x:c r="W49" s="4"/>
       <x:c r="X49" s="4"/>
       <x:c r="Y49" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z49" s="4"/>
       <x:c r="AA49" s="4"/>
@@ -9240,13 +9241,13 @@
       <x:c r="AC49" s="4"/>
       <x:c r="AD49" s="4"/>
       <x:c r="AE49" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:31">
       <x:c r="A50" s="4"/>
       <x:c r="B50" s="5" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C50" s="4"/>
       <x:c r="D50" s="4"/>
@@ -9257,29 +9258,29 @@
       <x:c r="I50" s="4"/>
       <x:c r="J50" s="4"/>
       <x:c r="K50" s="6" t="s">
-        <x:v>416</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="L50" s="4"/>
       <x:c r="M50" s="4"/>
       <x:c r="N50" s="6" t="s">
-        <x:v>417</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="O50" s="4"/>
       <x:c r="P50" s="4"/>
       <x:c r="Q50" s="6" t="s">
-        <x:v>418</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="R50" s="4"/>
       <x:c r="S50" s="4"/>
       <x:c r="T50" s="4"/>
       <x:c r="U50" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V50" s="4"/>
       <x:c r="W50" s="4"/>
       <x:c r="X50" s="4"/>
       <x:c r="Y50" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z50" s="4"/>
       <x:c r="AA50" s="4"/>
@@ -9287,13 +9288,13 @@
       <x:c r="AC50" s="4"/>
       <x:c r="AD50" s="4"/>
       <x:c r="AE50" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:31">
       <x:c r="A51" s="4"/>
       <x:c r="B51" s="5" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C51" s="4"/>
       <x:c r="D51" s="4"/>
@@ -9304,29 +9305,29 @@
       <x:c r="I51" s="4"/>
       <x:c r="J51" s="4"/>
       <x:c r="K51" s="6" t="s">
-        <x:v>419</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="L51" s="4"/>
       <x:c r="M51" s="4"/>
       <x:c r="N51" s="6" t="s">
-        <x:v>420</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="O51" s="4"/>
       <x:c r="P51" s="4"/>
       <x:c r="Q51" s="6" t="s">
-        <x:v>421</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="R51" s="4"/>
       <x:c r="S51" s="4"/>
       <x:c r="T51" s="4"/>
       <x:c r="U51" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V51" s="4"/>
       <x:c r="W51" s="4"/>
       <x:c r="X51" s="4"/>
       <x:c r="Y51" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z51" s="4"/>
       <x:c r="AA51" s="4"/>
@@ -9334,13 +9335,13 @@
       <x:c r="AC51" s="4"/>
       <x:c r="AD51" s="4"/>
       <x:c r="AE51" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:31">
       <x:c r="A52" s="4"/>
       <x:c r="B52" s="5" t="s">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C52" s="4"/>
       <x:c r="D52" s="4"/>
@@ -9351,29 +9352,29 @@
       <x:c r="I52" s="4"/>
       <x:c r="J52" s="4"/>
       <x:c r="K52" s="6" t="s">
-        <x:v>422</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="L52" s="4"/>
       <x:c r="M52" s="4"/>
       <x:c r="N52" s="6" t="s">
-        <x:v>423</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="O52" s="4"/>
       <x:c r="P52" s="4"/>
       <x:c r="Q52" s="6" t="s">
-        <x:v>424</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="R52" s="4"/>
       <x:c r="S52" s="4"/>
       <x:c r="T52" s="4"/>
       <x:c r="U52" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V52" s="4"/>
       <x:c r="W52" s="4"/>
       <x:c r="X52" s="4"/>
       <x:c r="Y52" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z52" s="4"/>
       <x:c r="AA52" s="4"/>
@@ -9381,13 +9382,13 @@
       <x:c r="AC52" s="4"/>
       <x:c r="AD52" s="4"/>
       <x:c r="AE52" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:31">
       <x:c r="A53" s="4"/>
       <x:c r="B53" s="5" t="s">
-        <x:v>425</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C53" s="4"/>
       <x:c r="D53" s="4"/>
@@ -9398,29 +9399,29 @@
       <x:c r="I53" s="4"/>
       <x:c r="J53" s="4"/>
       <x:c r="K53" s="6" t="s">
-        <x:v>426</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="L53" s="4"/>
       <x:c r="M53" s="4"/>
       <x:c r="N53" s="6" t="s">
-        <x:v>427</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="O53" s="4"/>
       <x:c r="P53" s="4"/>
       <x:c r="Q53" s="6" t="s">
-        <x:v>428</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="R53" s="4"/>
       <x:c r="S53" s="4"/>
       <x:c r="T53" s="4"/>
       <x:c r="U53" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V53" s="4"/>
       <x:c r="W53" s="4"/>
       <x:c r="X53" s="4"/>
       <x:c r="Y53" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z53" s="4"/>
       <x:c r="AA53" s="4"/>
@@ -9428,13 +9429,13 @@
       <x:c r="AC53" s="4"/>
       <x:c r="AD53" s="4"/>
       <x:c r="AE53" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:31">
       <x:c r="A54" s="4"/>
       <x:c r="B54" s="5" t="s">
-        <x:v>429</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C54" s="4"/>
       <x:c r="D54" s="4"/>
@@ -9445,29 +9446,29 @@
       <x:c r="I54" s="4"/>
       <x:c r="J54" s="4"/>
       <x:c r="K54" s="6" t="s">
-        <x:v>430</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="L54" s="4"/>
       <x:c r="M54" s="4"/>
       <x:c r="N54" s="6" t="s">
-        <x:v>431</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="O54" s="4"/>
       <x:c r="P54" s="4"/>
       <x:c r="Q54" s="6" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="R54" s="4"/>
       <x:c r="S54" s="4"/>
       <x:c r="T54" s="4"/>
       <x:c r="U54" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V54" s="4"/>
       <x:c r="W54" s="4"/>
       <x:c r="X54" s="4"/>
       <x:c r="Y54" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z54" s="4"/>
       <x:c r="AA54" s="4"/>
@@ -9475,13 +9476,13 @@
       <x:c r="AC54" s="4"/>
       <x:c r="AD54" s="4"/>
       <x:c r="AE54" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:31">
       <x:c r="A55" s="4"/>
       <x:c r="B55" s="5" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C55" s="4"/>
       <x:c r="D55" s="4"/>
@@ -9492,29 +9493,29 @@
       <x:c r="I55" s="4"/>
       <x:c r="J55" s="4"/>
       <x:c r="K55" s="6" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="L55" s="4"/>
       <x:c r="M55" s="4"/>
       <x:c r="N55" s="6" t="s">
-        <x:v>434</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="O55" s="4"/>
       <x:c r="P55" s="4"/>
       <x:c r="Q55" s="6" t="s">
-        <x:v>435</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="R55" s="4"/>
       <x:c r="S55" s="4"/>
       <x:c r="T55" s="4"/>
       <x:c r="U55" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V55" s="4"/>
       <x:c r="W55" s="4"/>
       <x:c r="X55" s="4"/>
       <x:c r="Y55" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z55" s="4"/>
       <x:c r="AA55" s="4"/>
@@ -9522,13 +9523,13 @@
       <x:c r="AC55" s="4"/>
       <x:c r="AD55" s="4"/>
       <x:c r="AE55" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:31">
       <x:c r="A56" s="4"/>
       <x:c r="B56" s="5" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C56" s="4"/>
       <x:c r="D56" s="4"/>
@@ -9539,29 +9540,29 @@
       <x:c r="I56" s="4"/>
       <x:c r="J56" s="4"/>
       <x:c r="K56" s="6" t="s">
-        <x:v>436</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="L56" s="4"/>
       <x:c r="M56" s="4"/>
       <x:c r="N56" s="6" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="O56" s="4"/>
       <x:c r="P56" s="4"/>
       <x:c r="Q56" s="6" t="s">
-        <x:v>438</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="R56" s="4"/>
       <x:c r="S56" s="4"/>
       <x:c r="T56" s="4"/>
       <x:c r="U56" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V56" s="4"/>
       <x:c r="W56" s="4"/>
       <x:c r="X56" s="4"/>
       <x:c r="Y56" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z56" s="4"/>
       <x:c r="AA56" s="4"/>
@@ -9569,13 +9570,13 @@
       <x:c r="AC56" s="4"/>
       <x:c r="AD56" s="4"/>
       <x:c r="AE56" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:31">
       <x:c r="A57" s="4"/>
       <x:c r="B57" s="5" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C57" s="4"/>
       <x:c r="D57" s="4"/>
@@ -9586,29 +9587,29 @@
       <x:c r="I57" s="4"/>
       <x:c r="J57" s="4"/>
       <x:c r="K57" s="6" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="L57" s="4"/>
       <x:c r="M57" s="4"/>
       <x:c r="N57" s="4"/>
       <x:c r="O57" s="6" t="s">
-        <x:v>441</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="P57" s="4"/>
       <x:c r="Q57" s="6" t="s">
-        <x:v>442</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="R57" s="4"/>
       <x:c r="S57" s="4"/>
       <x:c r="T57" s="4"/>
       <x:c r="U57" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V57" s="4"/>
       <x:c r="W57" s="4"/>
       <x:c r="X57" s="4"/>
       <x:c r="Y57" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z57" s="4"/>
       <x:c r="AA57" s="4"/>
@@ -9616,13 +9617,13 @@
       <x:c r="AC57" s="4"/>
       <x:c r="AD57" s="4"/>
       <x:c r="AE57" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:31">
       <x:c r="A58" s="4"/>
       <x:c r="B58" s="5" t="s">
-        <x:v>360</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C58" s="4"/>
       <x:c r="D58" s="4"/>
@@ -9633,29 +9634,29 @@
       <x:c r="I58" s="4"/>
       <x:c r="J58" s="4"/>
       <x:c r="K58" s="6" t="s">
-        <x:v>443</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="L58" s="4"/>
       <x:c r="M58" s="4"/>
       <x:c r="N58" s="4"/>
       <x:c r="O58" s="6" t="s">
-        <x:v>444</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="P58" s="4"/>
       <x:c r="Q58" s="6" t="s">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="R58" s="4"/>
       <x:c r="S58" s="4"/>
       <x:c r="T58" s="4"/>
       <x:c r="U58" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V58" s="4"/>
       <x:c r="W58" s="4"/>
       <x:c r="X58" s="4"/>
       <x:c r="Y58" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z58" s="4"/>
       <x:c r="AA58" s="4"/>
@@ -9663,7 +9664,7 @@
       <x:c r="AC58" s="4"/>
       <x:c r="AD58" s="4"/>
       <x:c r="AE58" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:31">
@@ -9682,7 +9683,7 @@
       <x:c r="M59" s="4"/>
       <x:c r="N59" s="4"/>
       <x:c r="O59" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="P59" s="4"/>
       <x:c r="Q59" s="4"/>
@@ -9712,28 +9713,28 @@
       <x:c r="H60" s="4"/>
       <x:c r="I60" s="4"/>
       <x:c r="J60" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K60" s="4"/>
       <x:c r="L60" s="4"/>
       <x:c r="M60" s="4"/>
       <x:c r="N60" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="O60" s="4"/>
       <x:c r="P60" s="4"/>
       <x:c r="Q60" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="R60" s="4"/>
       <x:c r="S60" s="4"/>
       <x:c r="T60" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="U60" s="4"/>
       <x:c r="V60" s="4"/>
       <x:c r="W60" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="X60" s="4"/>
       <x:c r="Y60" s="4"/>
@@ -9742,7 +9743,7 @@
       <x:c r="AB60" s="4"/>
       <x:c r="AC60" s="4"/>
       <x:c r="AD60" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AE60" s="4"/>
     </x:row>
@@ -9757,27 +9758,27 @@
       <x:c r="H61" s="4"/>
       <x:c r="I61" s="4"/>
       <x:c r="J61" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="K61" s="4"/>
       <x:c r="L61" s="4"/>
       <x:c r="M61" s="4"/>
       <x:c r="N61" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="O61" s="4"/>
       <x:c r="P61" s="4"/>
       <x:c r="Q61" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="R61" s="4"/>
       <x:c r="S61" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="T61" s="4"/>
       <x:c r="U61" s="4"/>
       <x:c r="V61" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="W61" s="4"/>
       <x:c r="X61" s="4"/>
@@ -9786,7 +9787,7 @@
       <x:c r="AA61" s="4"/>
       <x:c r="AB61" s="4"/>
       <x:c r="AC61" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AD61" s="4"/>
       <x:c r="AE61" s="4"/>
@@ -9796,7 +9797,7 @@
       <x:c r="B62" s="4"/>
       <x:c r="C62" s="4"/>
       <x:c r="D62" s="5" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="E62" s="4"/>
       <x:c r="F62" s="4"/>
@@ -9841,12 +9842,12 @@
       <x:c r="L63" s="4"/>
       <x:c r="M63" s="4"/>
       <x:c r="N63" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="O63" s="4"/>
       <x:c r="P63" s="4"/>
       <x:c r="Q63" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="R63" s="4"/>
       <x:c r="S63" s="4"/>
@@ -9854,7 +9855,7 @@
       <x:c r="U63" s="4"/>
       <x:c r="V63" s="4"/>
       <x:c r="W63" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="X63" s="4"/>
       <x:c r="Y63" s="4"/>
@@ -9863,14 +9864,14 @@
       <x:c r="AB63" s="4"/>
       <x:c r="AC63" s="4"/>
       <x:c r="AD63" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AE63" s="4"/>
     </x:row>
     <x:row r="64" spans="1:31">
       <x:c r="A64" s="4"/>
       <x:c r="B64" s="5" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C64" s="4"/>
       <x:c r="D64" s="4"/>
@@ -9881,28 +9882,28 @@
       <x:c r="I64" s="4"/>
       <x:c r="J64" s="4"/>
       <x:c r="K64" s="6" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="L64" s="4"/>
       <x:c r="M64" s="4"/>
       <x:c r="N64" s="6" t="s">
-        <x:v>446</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="O64" s="4"/>
       <x:c r="P64" s="4"/>
       <x:c r="Q64" s="6" t="s">
-        <x:v>447</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="R64" s="4"/>
       <x:c r="S64" s="4"/>
       <x:c r="T64" s="4"/>
       <x:c r="U64" s="6" t="s">
-        <x:v>448</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="V64" s="4"/>
       <x:c r="W64" s="4"/>
       <x:c r="X64" s="6" t="s">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="Y64" s="4"/>
       <x:c r="Z64" s="4"/>
@@ -9910,14 +9911,14 @@
       <x:c r="AB64" s="4"/>
       <x:c r="AC64" s="4"/>
       <x:c r="AD64" s="6" t="s">
-        <x:v>450</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="AE64" s="4"/>
     </x:row>
     <x:row r="65" spans="1:31">
       <x:c r="A65" s="4"/>
       <x:c r="B65" s="5" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C65" s="4"/>
       <x:c r="D65" s="4"/>
@@ -9928,28 +9929,28 @@
       <x:c r="I65" s="4"/>
       <x:c r="J65" s="4"/>
       <x:c r="K65" s="6" t="s">
-        <x:v>451</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="L65" s="4"/>
       <x:c r="M65" s="4"/>
       <x:c r="N65" s="6" t="s">
-        <x:v>452</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="O65" s="4"/>
       <x:c r="P65" s="4"/>
       <x:c r="Q65" s="6" t="s">
-        <x:v>453</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="R65" s="4"/>
       <x:c r="S65" s="4"/>
       <x:c r="T65" s="4"/>
       <x:c r="U65" s="6" t="s">
-        <x:v>454</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="V65" s="4"/>
       <x:c r="W65" s="4"/>
       <x:c r="X65" s="6" t="s">
-        <x:v>455</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="Y65" s="4"/>
       <x:c r="Z65" s="4"/>
@@ -9957,14 +9958,14 @@
       <x:c r="AB65" s="4"/>
       <x:c r="AC65" s="4"/>
       <x:c r="AD65" s="6" t="s">
-        <x:v>456</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="AE65" s="4"/>
     </x:row>
     <x:row r="66" spans="1:31">
       <x:c r="A66" s="4"/>
       <x:c r="B66" s="5" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C66" s="4"/>
       <x:c r="D66" s="4"/>
@@ -9975,29 +9976,29 @@
       <x:c r="I66" s="4"/>
       <x:c r="J66" s="4"/>
       <x:c r="K66" s="6" t="s">
-        <x:v>457</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="L66" s="4"/>
       <x:c r="M66" s="4"/>
       <x:c r="N66" s="6" t="s">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="O66" s="4"/>
       <x:c r="P66" s="4"/>
       <x:c r="Q66" s="6" t="s">
-        <x:v>459</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="R66" s="4"/>
       <x:c r="S66" s="4"/>
       <x:c r="T66" s="4"/>
       <x:c r="U66" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V66" s="4"/>
       <x:c r="W66" s="4"/>
       <x:c r="X66" s="4"/>
       <x:c r="Y66" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z66" s="4"/>
       <x:c r="AA66" s="4"/>
@@ -10005,13 +10006,13 @@
       <x:c r="AC66" s="4"/>
       <x:c r="AD66" s="4"/>
       <x:c r="AE66" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:31">
       <x:c r="A67" s="4"/>
       <x:c r="B67" s="5" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C67" s="4"/>
       <x:c r="D67" s="4"/>
@@ -10022,29 +10023,29 @@
       <x:c r="I67" s="4"/>
       <x:c r="J67" s="4"/>
       <x:c r="K67" s="6" t="s">
-        <x:v>460</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="L67" s="4"/>
       <x:c r="M67" s="4"/>
       <x:c r="N67" s="6" t="s">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="O67" s="4"/>
       <x:c r="P67" s="4"/>
       <x:c r="Q67" s="6" t="s">
-        <x:v>462</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="R67" s="4"/>
       <x:c r="S67" s="4"/>
       <x:c r="T67" s="4"/>
       <x:c r="U67" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="V67" s="4"/>
       <x:c r="W67" s="4"/>
       <x:c r="X67" s="4"/>
       <x:c r="Y67" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z67" s="4"/>
       <x:c r="AA67" s="4"/>
@@ -10052,13 +10053,13 @@
       <x:c r="AC67" s="4"/>
       <x:c r="AD67" s="4"/>
       <x:c r="AE67" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:31">
       <x:c r="A68" s="4"/>
       <x:c r="B68" s="5" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C68" s="4"/>
       <x:c r="D68" s="4"/>
@@ -10069,28 +10070,28 @@
       <x:c r="I68" s="4"/>
       <x:c r="J68" s="4"/>
       <x:c r="K68" s="6" t="s">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="L68" s="4"/>
       <x:c r="M68" s="4"/>
       <x:c r="N68" s="6" t="s">
-        <x:v>464</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="O68" s="4"/>
       <x:c r="P68" s="4"/>
       <x:c r="Q68" s="6" t="s">
-        <x:v>465</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="R68" s="4"/>
       <x:c r="S68" s="4"/>
       <x:c r="T68" s="4"/>
       <x:c r="U68" s="6" t="s">
-        <x:v>466</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="V68" s="4"/>
       <x:c r="W68" s="4"/>
       <x:c r="X68" s="6" t="s">
-        <x:v>467</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="Y68" s="4"/>
       <x:c r="Z68" s="4"/>
@@ -10098,26 +10099,26 @@
       <x:c r="AB68" s="4"/>
       <x:c r="AC68" s="4"/>
       <x:c r="AD68" s="6" t="s">
-        <x:v>468</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="AE68" s="4"/>
     </x:row>
     <x:row r="69" spans="1:31">
       <x:c r="A69" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B69" s="4"/>
       <x:c r="C69" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="D69" s="4"/>
       <x:c r="E69" s="4"/>
       <x:c r="F69" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G69" s="4"/>
       <x:c r="H69" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="I69" s="4"/>
       <x:c r="J69" s="4"/>
@@ -10140,13 +10141,13 @@
       <x:c r="AA69" s="4"/>
       <x:c r="AB69" s="4"/>
       <x:c r="AC69" s="5" t="s">
-        <x:v>469</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="AD69" s="4"/>
       <x:c r="AE69" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1"/>
+  <x:sheetProtection password="8CAE" sheet="1" objects="1"/>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AE1"/>
     <x:mergeCell ref="A2:AE2"/>
@@ -10209,7 +10210,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:41" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -10254,7 +10255,7 @@
     </x:row>
     <x:row r="2" spans="1:41" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -10300,7 +10301,7 @@
     <x:row r="3" spans="1:41">
       <x:c r="A3" s="4"/>
       <x:c r="B3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
@@ -10308,7 +10309,7 @@
       <x:c r="F3" s="4"/>
       <x:c r="G3" s="4"/>
       <x:c r="H3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I3" s="4"/>
       <x:c r="J3" s="4"/>
@@ -10326,7 +10327,7 @@
       <x:c r="V3" s="4"/>
       <x:c r="W3" s="4"/>
       <x:c r="X3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y3" s="4"/>
       <x:c r="Z3" s="4"/>
@@ -10340,7 +10341,7 @@
       <x:c r="AH3" s="4"/>
       <x:c r="AI3" s="4"/>
       <x:c r="AJ3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK3" s="4"/>
       <x:c r="AL3" s="4"/>
@@ -10351,7 +10352,7 @@
     <x:row r="4" spans="1:41">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -10364,7 +10365,7 @@
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="N4" s="4"/>
       <x:c r="O4" s="4"/>
@@ -10377,7 +10378,7 @@
       <x:c r="V4" s="4"/>
       <x:c r="W4" s="4"/>
       <x:c r="X4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="Y4" s="4"/>
       <x:c r="Z4" s="4"/>
@@ -10392,7 +10393,7 @@
       <x:c r="AI4" s="4"/>
       <x:c r="AJ4" s="4"/>
       <x:c r="AK4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AL4" s="4"/>
       <x:c r="AM4" s="4"/>
@@ -10402,7 +10403,7 @@
     <x:row r="5" spans="1:41">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -10415,7 +10416,7 @@
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="4"/>
       <x:c r="M5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="N5" s="4"/>
       <x:c r="O5" s="4"/>
@@ -10428,7 +10429,7 @@
       <x:c r="V5" s="4"/>
       <x:c r="W5" s="4"/>
       <x:c r="X5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="Y5" s="4"/>
       <x:c r="Z5" s="4"/>
@@ -10442,7 +10443,7 @@
       <x:c r="AH5" s="4"/>
       <x:c r="AI5" s="4"/>
       <x:c r="AJ5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="AK5" s="4"/>
       <x:c r="AL5" s="4"/>
@@ -10453,7 +10454,7 @@
     <x:row r="6" spans="1:41">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -10466,7 +10467,7 @@
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="N6" s="4"/>
       <x:c r="O6" s="4"/>
@@ -10479,7 +10480,7 @@
       <x:c r="V6" s="4"/>
       <x:c r="W6" s="4"/>
       <x:c r="X6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="Y6" s="4"/>
       <x:c r="Z6" s="4"/>
@@ -10495,7 +10496,7 @@
       <x:c r="AJ6" s="4"/>
       <x:c r="AK6" s="4"/>
       <x:c r="AL6" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AM6" s="4"/>
       <x:c r="AN6" s="4"/>
@@ -10504,7 +10505,7 @@
     <x:row r="7" spans="1:41">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -10513,7 +10514,7 @@
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
@@ -10530,7 +10531,7 @@
       <x:c r="V7" s="4"/>
       <x:c r="W7" s="4"/>
       <x:c r="X7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="Y7" s="4"/>
       <x:c r="Z7" s="4"/>
@@ -10546,7 +10547,7 @@
       <x:c r="AJ7" s="4"/>
       <x:c r="AK7" s="4"/>
       <x:c r="AL7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AM7" s="4"/>
       <x:c r="AN7" s="4"/>
@@ -10555,14 +10556,14 @@
     <x:row r="8" spans="1:41">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
@@ -10594,7 +10595,7 @@
       <x:c r="AI8" s="4"/>
       <x:c r="AJ8" s="4"/>
       <x:c r="AK8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AL8" s="4"/>
       <x:c r="AM8" s="4"/>
@@ -10622,7 +10623,7 @@
       <x:c r="R9" s="4"/>
       <x:c r="S9" s="4"/>
       <x:c r="T9" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="U9" s="4"/>
       <x:c r="V9" s="4"/>
@@ -10661,33 +10662,33 @@
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
       <x:c r="N10" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="4"/>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="T10" s="4"/>
       <x:c r="U10" s="4"/>
       <x:c r="V10" s="4"/>
       <x:c r="W10" s="4"/>
       <x:c r="X10" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="Y10" s="4"/>
       <x:c r="Z10" s="4"/>
       <x:c r="AA10" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="AB10" s="4"/>
       <x:c r="AC10" s="4"/>
       <x:c r="AD10" s="4"/>
       <x:c r="AE10" s="4"/>
       <x:c r="AF10" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AG10" s="4"/>
       <x:c r="AH10" s="4"/>
@@ -10697,7 +10698,7 @@
       <x:c r="AL10" s="4"/>
       <x:c r="AM10" s="4"/>
       <x:c r="AN10" s="5" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="AO10" s="4"/>
     </x:row>
@@ -10716,32 +10717,32 @@
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="4"/>
       <x:c r="N11" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="4"/>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
       <x:c r="S11" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="T11" s="4"/>
       <x:c r="U11" s="4"/>
       <x:c r="V11" s="4"/>
       <x:c r="W11" s="5" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="X11" s="4"/>
       <x:c r="Y11" s="4"/>
       <x:c r="Z11" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AA11" s="4"/>
       <x:c r="AB11" s="4"/>
       <x:c r="AC11" s="4"/>
       <x:c r="AD11" s="4"/>
       <x:c r="AE11" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AF11" s="4"/>
       <x:c r="AG11" s="4"/>
@@ -10751,7 +10752,7 @@
       <x:c r="AK11" s="4"/>
       <x:c r="AL11" s="4"/>
       <x:c r="AM11" s="5" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AN11" s="4"/>
       <x:c r="AO11" s="4"/>
@@ -10763,7 +10764,7 @@
       <x:c r="D12" s="4"/>
       <x:c r="E12" s="4"/>
       <x:c r="F12" s="5" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
@@ -10821,14 +10822,14 @@
       <x:c r="Q13" s="4"/>
       <x:c r="R13" s="4"/>
       <x:c r="S13" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="T13" s="4"/>
       <x:c r="U13" s="4"/>
       <x:c r="V13" s="4"/>
       <x:c r="W13" s="4"/>
       <x:c r="X13" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="Y13" s="4"/>
       <x:c r="Z13" s="4"/>
@@ -10838,7 +10839,7 @@
       <x:c r="AD13" s="4"/>
       <x:c r="AE13" s="4"/>
       <x:c r="AF13" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AG13" s="4"/>
       <x:c r="AH13" s="4"/>
@@ -10848,14 +10849,14 @@
       <x:c r="AL13" s="4"/>
       <x:c r="AM13" s="4"/>
       <x:c r="AN13" s="5" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="AO13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:41">
       <x:c r="A14" s="4"/>
       <x:c r="B14" s="5" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="4"/>
@@ -10870,33 +10871,33 @@
       <x:c r="M14" s="4"/>
       <x:c r="N14" s="4"/>
       <x:c r="O14" s="6" t="s">
-        <x:v>470</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="P14" s="4"/>
       <x:c r="Q14" s="4"/>
       <x:c r="R14" s="4"/>
       <x:c r="S14" s="6" t="s">
-        <x:v>471</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="T14" s="4"/>
       <x:c r="U14" s="4"/>
       <x:c r="V14" s="4"/>
       <x:c r="W14" s="4"/>
       <x:c r="X14" s="6" t="s">
-        <x:v>472</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="Y14" s="4"/>
       <x:c r="Z14" s="4"/>
       <x:c r="AA14" s="4"/>
       <x:c r="AB14" s="6" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="AC14" s="4"/>
       <x:c r="AD14" s="4"/>
       <x:c r="AE14" s="4"/>
       <x:c r="AF14" s="4"/>
       <x:c r="AG14" s="6" t="s">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="AH14" s="4"/>
       <x:c r="AI14" s="4"/>
@@ -10905,14 +10906,14 @@
       <x:c r="AL14" s="4"/>
       <x:c r="AM14" s="4"/>
       <x:c r="AN14" s="6" t="s">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="AO14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:41">
       <x:c r="A15" s="4"/>
       <x:c r="B15" s="5" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -10927,33 +10928,33 @@
       <x:c r="M15" s="4"/>
       <x:c r="N15" s="4"/>
       <x:c r="O15" s="6" t="s">
-        <x:v>470</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="4"/>
       <x:c r="S15" s="6" t="s">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T15" s="4"/>
       <x:c r="U15" s="4"/>
       <x:c r="V15" s="4"/>
       <x:c r="W15" s="4"/>
       <x:c r="X15" s="6" t="s">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="Y15" s="4"/>
       <x:c r="Z15" s="4"/>
       <x:c r="AA15" s="4"/>
       <x:c r="AB15" s="6" t="s">
-        <x:v>477</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="AC15" s="4"/>
       <x:c r="AD15" s="4"/>
       <x:c r="AE15" s="4"/>
       <x:c r="AF15" s="4"/>
       <x:c r="AG15" s="6" t="s">
-        <x:v>478</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="AH15" s="4"/>
       <x:c r="AI15" s="4"/>
@@ -10962,14 +10963,14 @@
       <x:c r="AL15" s="4"/>
       <x:c r="AM15" s="4"/>
       <x:c r="AN15" s="6" t="s">
-        <x:v>479</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="AO15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:41">
       <x:c r="A16" s="4"/>
       <x:c r="B16" s="5" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
@@ -10984,33 +10985,33 @@
       <x:c r="M16" s="4"/>
       <x:c r="N16" s="4"/>
       <x:c r="O16" s="6" t="s">
-        <x:v>480</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="P16" s="4"/>
       <x:c r="Q16" s="4"/>
       <x:c r="R16" s="4"/>
       <x:c r="S16" s="6" t="s">
-        <x:v>481</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="T16" s="4"/>
       <x:c r="U16" s="4"/>
       <x:c r="V16" s="4"/>
       <x:c r="W16" s="4"/>
       <x:c r="X16" s="6" t="s">
-        <x:v>482</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="Y16" s="4"/>
       <x:c r="Z16" s="4"/>
       <x:c r="AA16" s="4"/>
       <x:c r="AB16" s="6" t="s">
-        <x:v>483</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="AC16" s="4"/>
       <x:c r="AD16" s="4"/>
       <x:c r="AE16" s="4"/>
       <x:c r="AF16" s="4"/>
       <x:c r="AG16" s="6" t="s">
-        <x:v>484</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="AH16" s="4"/>
       <x:c r="AI16" s="4"/>
@@ -11019,14 +11020,14 @@
       <x:c r="AL16" s="4"/>
       <x:c r="AM16" s="4"/>
       <x:c r="AN16" s="6" t="s">
-        <x:v>485</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="AO16" s="4"/>
     </x:row>
     <x:row r="17" spans="1:41">
       <x:c r="A17" s="4"/>
       <x:c r="B17" s="5" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="4"/>
@@ -11041,26 +11042,26 @@
       <x:c r="M17" s="4"/>
       <x:c r="N17" s="4"/>
       <x:c r="O17" s="6" t="s">
-        <x:v>486</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="P17" s="4"/>
       <x:c r="Q17" s="4"/>
       <x:c r="R17" s="4"/>
       <x:c r="S17" s="6" t="s">
-        <x:v>487</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="T17" s="4"/>
       <x:c r="U17" s="4"/>
       <x:c r="V17" s="4"/>
       <x:c r="W17" s="4"/>
       <x:c r="X17" s="6" t="s">
-        <x:v>488</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="Y17" s="4"/>
       <x:c r="Z17" s="4"/>
       <x:c r="AA17" s="4"/>
       <x:c r="AB17" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC17" s="4"/>
       <x:c r="AD17" s="4"/>
@@ -11068,7 +11069,7 @@
       <x:c r="AF17" s="4"/>
       <x:c r="AG17" s="4"/>
       <x:c r="AH17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI17" s="4"/>
       <x:c r="AJ17" s="4"/>
@@ -11077,13 +11078,13 @@
       <x:c r="AM17" s="4"/>
       <x:c r="AN17" s="4"/>
       <x:c r="AO17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:41">
       <x:c r="A18" s="4"/>
       <x:c r="B18" s="5" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C18" s="4"/>
       <x:c r="D18" s="4"/>
@@ -11098,26 +11099,26 @@
       <x:c r="M18" s="4"/>
       <x:c r="N18" s="4"/>
       <x:c r="O18" s="6" t="s">
-        <x:v>489</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="P18" s="4"/>
       <x:c r="Q18" s="4"/>
       <x:c r="R18" s="4"/>
       <x:c r="S18" s="6" t="s">
-        <x:v>490</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="T18" s="4"/>
       <x:c r="U18" s="4"/>
       <x:c r="V18" s="4"/>
       <x:c r="W18" s="4"/>
       <x:c r="X18" s="6" t="s">
-        <x:v>491</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="Y18" s="4"/>
       <x:c r="Z18" s="4"/>
       <x:c r="AA18" s="4"/>
       <x:c r="AB18" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC18" s="4"/>
       <x:c r="AD18" s="4"/>
@@ -11125,7 +11126,7 @@
       <x:c r="AF18" s="4"/>
       <x:c r="AG18" s="4"/>
       <x:c r="AH18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI18" s="4"/>
       <x:c r="AJ18" s="4"/>
@@ -11134,13 +11135,13 @@
       <x:c r="AM18" s="4"/>
       <x:c r="AN18" s="4"/>
       <x:c r="AO18" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:41">
       <x:c r="A19" s="4"/>
       <x:c r="B19" s="5" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C19" s="4"/>
       <x:c r="D19" s="4"/>
@@ -11155,26 +11156,26 @@
       <x:c r="M19" s="4"/>
       <x:c r="N19" s="4"/>
       <x:c r="O19" s="6" t="s">
-        <x:v>492</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="P19" s="4"/>
       <x:c r="Q19" s="4"/>
       <x:c r="R19" s="4"/>
       <x:c r="S19" s="6" t="s">
-        <x:v>493</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="T19" s="4"/>
       <x:c r="U19" s="4"/>
       <x:c r="V19" s="4"/>
       <x:c r="W19" s="4"/>
       <x:c r="X19" s="6" t="s">
-        <x:v>494</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="Y19" s="4"/>
       <x:c r="Z19" s="4"/>
       <x:c r="AA19" s="4"/>
       <x:c r="AB19" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC19" s="4"/>
       <x:c r="AD19" s="4"/>
@@ -11182,7 +11183,7 @@
       <x:c r="AF19" s="4"/>
       <x:c r="AG19" s="4"/>
       <x:c r="AH19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI19" s="4"/>
       <x:c r="AJ19" s="4"/>
@@ -11191,13 +11192,13 @@
       <x:c r="AM19" s="4"/>
       <x:c r="AN19" s="4"/>
       <x:c r="AO19" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:41">
       <x:c r="A20" s="4"/>
       <x:c r="B20" s="5" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C20" s="4"/>
       <x:c r="D20" s="4"/>
@@ -11212,26 +11213,26 @@
       <x:c r="M20" s="4"/>
       <x:c r="N20" s="4"/>
       <x:c r="O20" s="6" t="s">
-        <x:v>495</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="P20" s="4"/>
       <x:c r="Q20" s="4"/>
       <x:c r="R20" s="4"/>
       <x:c r="S20" s="6" t="s">
-        <x:v>496</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="T20" s="4"/>
       <x:c r="U20" s="4"/>
       <x:c r="V20" s="4"/>
       <x:c r="W20" s="4"/>
       <x:c r="X20" s="6" t="s">
-        <x:v>497</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="Y20" s="4"/>
       <x:c r="Z20" s="4"/>
       <x:c r="AA20" s="4"/>
       <x:c r="AB20" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC20" s="4"/>
       <x:c r="AD20" s="4"/>
@@ -11239,7 +11240,7 @@
       <x:c r="AF20" s="4"/>
       <x:c r="AG20" s="4"/>
       <x:c r="AH20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI20" s="4"/>
       <x:c r="AJ20" s="4"/>
@@ -11248,13 +11249,13 @@
       <x:c r="AM20" s="4"/>
       <x:c r="AN20" s="4"/>
       <x:c r="AO20" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:41">
       <x:c r="A21" s="4"/>
       <x:c r="B21" s="5" t="s">
-        <x:v>498</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C21" s="4"/>
       <x:c r="D21" s="4"/>
@@ -11269,26 +11270,26 @@
       <x:c r="M21" s="4"/>
       <x:c r="N21" s="4"/>
       <x:c r="O21" s="6" t="s">
-        <x:v>499</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="P21" s="4"/>
       <x:c r="Q21" s="4"/>
       <x:c r="R21" s="4"/>
       <x:c r="S21" s="6" t="s">
-        <x:v>500</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="T21" s="4"/>
       <x:c r="U21" s="4"/>
       <x:c r="V21" s="4"/>
       <x:c r="W21" s="4"/>
       <x:c r="X21" s="6" t="s">
-        <x:v>501</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="Y21" s="4"/>
       <x:c r="Z21" s="4"/>
       <x:c r="AA21" s="4"/>
       <x:c r="AB21" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC21" s="4"/>
       <x:c r="AD21" s="4"/>
@@ -11296,7 +11297,7 @@
       <x:c r="AF21" s="4"/>
       <x:c r="AG21" s="4"/>
       <x:c r="AH21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI21" s="4"/>
       <x:c r="AJ21" s="4"/>
@@ -11305,13 +11306,13 @@
       <x:c r="AM21" s="4"/>
       <x:c r="AN21" s="4"/>
       <x:c r="AO21" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:41">
       <x:c r="A22" s="4"/>
       <x:c r="B22" s="5" t="s">
-        <x:v>502</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="C22" s="4"/>
       <x:c r="D22" s="4"/>
@@ -11326,33 +11327,33 @@
       <x:c r="M22" s="4"/>
       <x:c r="N22" s="4"/>
       <x:c r="O22" s="6" t="s">
-        <x:v>503</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="P22" s="4"/>
       <x:c r="Q22" s="4"/>
       <x:c r="R22" s="4"/>
       <x:c r="S22" s="4"/>
       <x:c r="T22" s="6" t="s">
-        <x:v>504</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="U22" s="4"/>
       <x:c r="V22" s="4"/>
       <x:c r="W22" s="4"/>
       <x:c r="X22" s="6" t="s">
-        <x:v>505</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="Y22" s="4"/>
       <x:c r="Z22" s="4"/>
       <x:c r="AA22" s="4"/>
       <x:c r="AB22" s="6" t="s">
-        <x:v>506</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="AC22" s="4"/>
       <x:c r="AD22" s="4"/>
       <x:c r="AE22" s="4"/>
       <x:c r="AF22" s="4"/>
       <x:c r="AG22" s="6" t="s">
-        <x:v>507</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="AH22" s="4"/>
       <x:c r="AI22" s="4"/>
@@ -11361,14 +11362,14 @@
       <x:c r="AL22" s="4"/>
       <x:c r="AM22" s="4"/>
       <x:c r="AN22" s="6" t="s">
-        <x:v>508</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="AO22" s="4"/>
     </x:row>
     <x:row r="23" spans="1:41">
       <x:c r="A23" s="4"/>
       <x:c r="B23" s="5" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C23" s="4"/>
       <x:c r="D23" s="4"/>
@@ -11383,33 +11384,33 @@
       <x:c r="M23" s="4"/>
       <x:c r="N23" s="4"/>
       <x:c r="O23" s="6" t="s">
-        <x:v>509</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="P23" s="4"/>
       <x:c r="Q23" s="4"/>
       <x:c r="R23" s="4"/>
       <x:c r="S23" s="4"/>
       <x:c r="T23" s="6" t="s">
-        <x:v>510</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="U23" s="4"/>
       <x:c r="V23" s="4"/>
       <x:c r="W23" s="4"/>
       <x:c r="X23" s="6" t="s">
-        <x:v>511</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="Y23" s="4"/>
       <x:c r="Z23" s="4"/>
       <x:c r="AA23" s="4"/>
       <x:c r="AB23" s="6" t="s">
-        <x:v>512</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="AC23" s="4"/>
       <x:c r="AD23" s="4"/>
       <x:c r="AE23" s="4"/>
       <x:c r="AF23" s="4"/>
       <x:c r="AG23" s="6" t="s">
-        <x:v>513</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="AH23" s="4"/>
       <x:c r="AI23" s="4"/>
@@ -11418,14 +11419,14 @@
       <x:c r="AL23" s="4"/>
       <x:c r="AM23" s="4"/>
       <x:c r="AN23" s="6" t="s">
-        <x:v>514</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="AO23" s="4"/>
     </x:row>
     <x:row r="24" spans="1:41">
       <x:c r="A24" s="4"/>
       <x:c r="B24" s="5" t="s">
-        <x:v>515</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C24" s="4"/>
       <x:c r="D24" s="4"/>
@@ -11440,33 +11441,33 @@
       <x:c r="M24" s="4"/>
       <x:c r="N24" s="4"/>
       <x:c r="O24" s="6" t="s">
-        <x:v>516</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="P24" s="4"/>
       <x:c r="Q24" s="4"/>
       <x:c r="R24" s="4"/>
       <x:c r="S24" s="4"/>
       <x:c r="T24" s="6" t="s">
-        <x:v>517</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="U24" s="4"/>
       <x:c r="V24" s="4"/>
       <x:c r="W24" s="4"/>
       <x:c r="X24" s="6" t="s">
-        <x:v>518</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="Y24" s="4"/>
       <x:c r="Z24" s="4"/>
       <x:c r="AA24" s="4"/>
       <x:c r="AB24" s="6" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="AC24" s="4"/>
       <x:c r="AD24" s="4"/>
       <x:c r="AE24" s="4"/>
       <x:c r="AF24" s="4"/>
       <x:c r="AG24" s="6" t="s">
-        <x:v>519</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="AH24" s="4"/>
       <x:c r="AI24" s="4"/>
@@ -11475,14 +11476,14 @@
       <x:c r="AL24" s="4"/>
       <x:c r="AM24" s="4"/>
       <x:c r="AN24" s="6" t="s">
-        <x:v>520</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="AO24" s="4"/>
     </x:row>
     <x:row r="25" spans="1:41">
       <x:c r="A25" s="4"/>
       <x:c r="B25" s="5" t="s">
-        <x:v>521</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C25" s="4"/>
       <x:c r="D25" s="4"/>
@@ -11497,33 +11498,33 @@
       <x:c r="M25" s="4"/>
       <x:c r="N25" s="4"/>
       <x:c r="O25" s="6" t="s">
-        <x:v>522</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="P25" s="4"/>
       <x:c r="Q25" s="4"/>
       <x:c r="R25" s="4"/>
       <x:c r="S25" s="4"/>
       <x:c r="T25" s="6" t="s">
-        <x:v>523</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="U25" s="4"/>
       <x:c r="V25" s="4"/>
       <x:c r="W25" s="4"/>
       <x:c r="X25" s="6" t="s">
-        <x:v>524</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="Y25" s="4"/>
       <x:c r="Z25" s="4"/>
       <x:c r="AA25" s="4"/>
       <x:c r="AB25" s="6" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="AC25" s="4"/>
       <x:c r="AD25" s="4"/>
       <x:c r="AE25" s="4"/>
       <x:c r="AF25" s="4"/>
       <x:c r="AG25" s="6" t="s">
-        <x:v>525</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="AH25" s="4"/>
       <x:c r="AI25" s="4"/>
@@ -11532,14 +11533,14 @@
       <x:c r="AL25" s="4"/>
       <x:c r="AM25" s="4"/>
       <x:c r="AN25" s="6" t="s">
-        <x:v>526</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="AO25" s="4"/>
     </x:row>
     <x:row r="26" spans="1:41">
       <x:c r="A26" s="4"/>
       <x:c r="B26" s="5" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C26" s="4"/>
       <x:c r="D26" s="4"/>
@@ -11554,33 +11555,33 @@
       <x:c r="M26" s="4"/>
       <x:c r="N26" s="4"/>
       <x:c r="O26" s="6" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="P26" s="4"/>
       <x:c r="Q26" s="4"/>
       <x:c r="R26" s="4"/>
       <x:c r="S26" s="4"/>
       <x:c r="T26" s="6" t="s">
-        <x:v>529</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="U26" s="4"/>
       <x:c r="V26" s="4"/>
       <x:c r="W26" s="4"/>
       <x:c r="X26" s="6" t="s">
-        <x:v>530</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="Y26" s="4"/>
       <x:c r="Z26" s="4"/>
       <x:c r="AA26" s="4"/>
       <x:c r="AB26" s="6" t="s">
-        <x:v>531</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="AC26" s="4"/>
       <x:c r="AD26" s="4"/>
       <x:c r="AE26" s="4"/>
       <x:c r="AF26" s="4"/>
       <x:c r="AG26" s="6" t="s">
-        <x:v>532</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="AH26" s="4"/>
       <x:c r="AI26" s="4"/>
@@ -11589,14 +11590,14 @@
       <x:c r="AL26" s="4"/>
       <x:c r="AM26" s="4"/>
       <x:c r="AN26" s="6" t="s">
-        <x:v>533</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="AO26" s="4"/>
     </x:row>
     <x:row r="27" spans="1:41">
       <x:c r="A27" s="4"/>
       <x:c r="B27" s="5" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
@@ -11611,26 +11612,26 @@
       <x:c r="M27" s="4"/>
       <x:c r="N27" s="4"/>
       <x:c r="O27" s="6" t="s">
-        <x:v>534</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="P27" s="4"/>
       <x:c r="Q27" s="4"/>
       <x:c r="R27" s="4"/>
       <x:c r="S27" s="4"/>
       <x:c r="T27" s="6" t="s">
-        <x:v>535</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="U27" s="4"/>
       <x:c r="V27" s="4"/>
       <x:c r="W27" s="4"/>
       <x:c r="X27" s="6" t="s">
-        <x:v>536</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="Y27" s="4"/>
       <x:c r="Z27" s="4"/>
       <x:c r="AA27" s="4"/>
       <x:c r="AB27" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC27" s="4"/>
       <x:c r="AD27" s="4"/>
@@ -11638,7 +11639,7 @@
       <x:c r="AF27" s="4"/>
       <x:c r="AG27" s="4"/>
       <x:c r="AH27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI27" s="4"/>
       <x:c r="AJ27" s="4"/>
@@ -11647,13 +11648,13 @@
       <x:c r="AM27" s="4"/>
       <x:c r="AN27" s="4"/>
       <x:c r="AO27" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:41">
       <x:c r="A28" s="4"/>
       <x:c r="B28" s="5" t="s">
-        <x:v>537</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="C28" s="4"/>
       <x:c r="D28" s="4"/>
@@ -11668,26 +11669,26 @@
       <x:c r="M28" s="4"/>
       <x:c r="N28" s="4"/>
       <x:c r="O28" s="6" t="s">
-        <x:v>538</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="P28" s="4"/>
       <x:c r="Q28" s="4"/>
       <x:c r="R28" s="4"/>
       <x:c r="S28" s="4"/>
       <x:c r="T28" s="6" t="s">
-        <x:v>539</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="U28" s="4"/>
       <x:c r="V28" s="4"/>
       <x:c r="W28" s="4"/>
       <x:c r="X28" s="6" t="s">
-        <x:v>540</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="Y28" s="4"/>
       <x:c r="Z28" s="4"/>
       <x:c r="AA28" s="4"/>
       <x:c r="AB28" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AC28" s="4"/>
       <x:c r="AD28" s="4"/>
@@ -11695,7 +11696,7 @@
       <x:c r="AF28" s="4"/>
       <x:c r="AG28" s="4"/>
       <x:c r="AH28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AI28" s="4"/>
       <x:c r="AJ28" s="4"/>
@@ -11704,7 +11705,7 @@
       <x:c r="AM28" s="4"/>
       <x:c r="AN28" s="4"/>
       <x:c r="AO28" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:41">
@@ -11722,7 +11723,7 @@
       <x:c r="L29" s="4"/>
       <x:c r="M29" s="4"/>
       <x:c r="N29" s="5" t="s">
-        <x:v>541</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="O29" s="4"/>
       <x:c r="P29" s="4"/>
@@ -11770,7 +11771,7 @@
       <x:c r="O30" s="4"/>
       <x:c r="P30" s="4"/>
       <x:c r="Q30" s="5" t="s">
-        <x:v>542</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="R30" s="4"/>
       <x:c r="S30" s="4"/>
@@ -11820,7 +11821,7 @@
       <x:c r="T31" s="4"/>
       <x:c r="U31" s="4"/>
       <x:c r="V31" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="W31" s="4"/>
       <x:c r="X31" s="4"/>
@@ -11845,12 +11846,12 @@
     <x:row r="32" spans="1:41">
       <x:c r="A32" s="4"/>
       <x:c r="B32" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C32" s="4"/>
       <x:c r="D32" s="4"/>
       <x:c r="E32" s="5" t="s">
-        <x:v>544</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F32" s="4"/>
       <x:c r="G32" s="4"/>
@@ -11859,7 +11860,7 @@
       <x:c r="J32" s="4"/>
       <x:c r="K32" s="4"/>
       <x:c r="L32" s="5" t="s">
-        <x:v>545</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="M32" s="4"/>
       <x:c r="N32" s="4"/>
@@ -11870,15 +11871,15 @@
       <x:c r="S32" s="4"/>
       <x:c r="T32" s="4"/>
       <x:c r="U32" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="V32" s="4"/>
       <x:c r="W32" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="X32" s="4"/>
       <x:c r="Y32" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="Z32" s="4"/>
       <x:c r="AA32" s="4"/>
@@ -11887,7 +11888,7 @@
       <x:c r="AD32" s="4"/>
       <x:c r="AE32" s="4"/>
       <x:c r="AF32" s="5" t="s">
-        <x:v>546</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="AG32" s="4"/>
       <x:c r="AH32" s="4"/>
@@ -11902,20 +11903,20 @@
     <x:row r="33" spans="1:41">
       <x:c r="A33" s="4"/>
       <x:c r="B33" s="5" t="s">
-        <x:v>547</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C33" s="4"/>
       <x:c r="D33" s="4"/>
       <x:c r="E33" s="4"/>
       <x:c r="F33" s="5" t="s">
-        <x:v>548</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="G33" s="4"/>
       <x:c r="H33" s="4"/>
       <x:c r="I33" s="4"/>
       <x:c r="J33" s="4"/>
       <x:c r="K33" s="5" t="s">
-        <x:v>549</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="L33" s="4"/>
       <x:c r="M33" s="4"/>
@@ -11927,15 +11928,15 @@
       <x:c r="S33" s="4"/>
       <x:c r="T33" s="4"/>
       <x:c r="U33" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="V33" s="4"/>
       <x:c r="W33" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="X33" s="4"/>
       <x:c r="Y33" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="Z33" s="4"/>
       <x:c r="AA33" s="4"/>
@@ -11944,7 +11945,7 @@
       <x:c r="AD33" s="4"/>
       <x:c r="AE33" s="4"/>
       <x:c r="AF33" s="5" t="s">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="AG33" s="4"/>
       <x:c r="AH33" s="4"/>
@@ -11992,7 +11993,7 @@
       <x:c r="AG34" s="4"/>
       <x:c r="AH34" s="4"/>
       <x:c r="AI34" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AJ34" s="4"/>
       <x:c r="AK34" s="4"/>
@@ -12005,12 +12006,12 @@
       <x:c r="A35" s="4"/>
       <x:c r="B35" s="4"/>
       <x:c r="C35" s="5" t="s">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D35" s="4"/>
       <x:c r="E35" s="4"/>
       <x:c r="F35" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G35" s="4"/>
       <x:c r="H35" s="4"/>
@@ -12038,7 +12039,7 @@
       <x:c r="AD35" s="4"/>
       <x:c r="AE35" s="4"/>
       <x:c r="AF35" s="5" t="s">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="AG35" s="4"/>
       <x:c r="AH35" s="4"/>
@@ -12053,18 +12054,18 @@
     <x:row r="36" spans="1:41">
       <x:c r="A36" s="4"/>
       <x:c r="B36" s="5" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C36" s="4"/>
       <x:c r="D36" s="4"/>
       <x:c r="E36" s="5" t="s">
-        <x:v>555</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="F36" s="4"/>
       <x:c r="G36" s="4"/>
       <x:c r="H36" s="4"/>
       <x:c r="I36" s="5" t="s">
-        <x:v>556</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="J36" s="4"/>
       <x:c r="K36" s="4"/>
@@ -12077,23 +12078,23 @@
       <x:c r="R36" s="4"/>
       <x:c r="S36" s="4"/>
       <x:c r="T36" s="5" t="s">
-        <x:v>557</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="U36" s="4"/>
       <x:c r="V36" s="4"/>
       <x:c r="W36" s="5" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="X36" s="4"/>
       <x:c r="Y36" s="5" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Z36" s="4"/>
       <x:c r="AA36" s="4"/>
       <x:c r="AB36" s="4"/>
       <x:c r="AC36" s="4"/>
       <x:c r="AD36" s="5" t="s">
-        <x:v>560</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="AE36" s="4"/>
       <x:c r="AF36" s="4"/>
@@ -12142,7 +12143,7 @@
       <x:c r="AF37" s="4"/>
       <x:c r="AG37" s="4"/>
       <x:c r="AH37" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AI37" s="4"/>
       <x:c r="AJ37" s="4"/>
@@ -12169,7 +12170,7 @@
       <x:c r="N38" s="4"/>
       <x:c r="O38" s="4"/>
       <x:c r="P38" s="5" t="s">
-        <x:v>561</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="Q38" s="4"/>
       <x:c r="R38" s="4"/>
@@ -12219,7 +12220,7 @@
       <x:c r="S39" s="4"/>
       <x:c r="T39" s="4"/>
       <x:c r="U39" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V39" s="4"/>
       <x:c r="W39" s="4"/>
@@ -12245,12 +12246,12 @@
     <x:row r="40" spans="1:41">
       <x:c r="A40" s="4"/>
       <x:c r="B40" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C40" s="4"/>
       <x:c r="D40" s="4"/>
       <x:c r="E40" s="5" t="s">
-        <x:v>544</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F40" s="4"/>
       <x:c r="G40" s="4"/>
@@ -12259,7 +12260,7 @@
       <x:c r="J40" s="4"/>
       <x:c r="K40" s="4"/>
       <x:c r="L40" s="5" t="s">
-        <x:v>545</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="M40" s="4"/>
       <x:c r="N40" s="4"/>
@@ -12270,15 +12271,15 @@
       <x:c r="S40" s="4"/>
       <x:c r="T40" s="4"/>
       <x:c r="U40" s="5" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="V40" s="4"/>
       <x:c r="W40" s="5" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="X40" s="4"/>
       <x:c r="Y40" s="5" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="Z40" s="4"/>
       <x:c r="AA40" s="4"/>
@@ -12287,7 +12288,7 @@
       <x:c r="AD40" s="4"/>
       <x:c r="AE40" s="4"/>
       <x:c r="AF40" s="5" t="s">
-        <x:v>546</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="AG40" s="4"/>
       <x:c r="AH40" s="4"/>
@@ -12302,20 +12303,20 @@
     <x:row r="41" spans="1:41">
       <x:c r="A41" s="4"/>
       <x:c r="B41" s="5" t="s">
-        <x:v>547</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C41" s="4"/>
       <x:c r="D41" s="4"/>
       <x:c r="E41" s="4"/>
       <x:c r="F41" s="5" t="s">
-        <x:v>548</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="G41" s="4"/>
       <x:c r="H41" s="4"/>
       <x:c r="I41" s="4"/>
       <x:c r="J41" s="4"/>
       <x:c r="K41" s="5" t="s">
-        <x:v>549</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="L41" s="4"/>
       <x:c r="M41" s="4"/>
@@ -12327,15 +12328,15 @@
       <x:c r="S41" s="4"/>
       <x:c r="T41" s="4"/>
       <x:c r="U41" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="V41" s="4"/>
       <x:c r="W41" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="X41" s="4"/>
       <x:c r="Y41" s="5" t="s">
-        <x:v>550</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="Z41" s="4"/>
       <x:c r="AA41" s="4"/>
@@ -12344,7 +12345,7 @@
       <x:c r="AD41" s="4"/>
       <x:c r="AE41" s="4"/>
       <x:c r="AF41" s="5" t="s">
-        <x:v>551</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="AG41" s="4"/>
       <x:c r="AH41" s="4"/>
@@ -12392,7 +12393,7 @@
       <x:c r="AG42" s="4"/>
       <x:c r="AH42" s="4"/>
       <x:c r="AI42" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AJ42" s="4"/>
       <x:c r="AK42" s="4"/>
@@ -12405,12 +12406,12 @@
       <x:c r="A43" s="4"/>
       <x:c r="B43" s="4"/>
       <x:c r="C43" s="5" t="s">
-        <x:v>552</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D43" s="4"/>
       <x:c r="E43" s="4"/>
       <x:c r="F43" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G43" s="4"/>
       <x:c r="H43" s="4"/>
@@ -12438,7 +12439,7 @@
       <x:c r="AD43" s="4"/>
       <x:c r="AE43" s="4"/>
       <x:c r="AF43" s="5" t="s">
-        <x:v>553</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="AG43" s="4"/>
       <x:c r="AH43" s="4"/>
@@ -12453,18 +12454,18 @@
     <x:row r="44" spans="1:41">
       <x:c r="A44" s="4"/>
       <x:c r="B44" s="5" t="s">
-        <x:v>554</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C44" s="4"/>
       <x:c r="D44" s="4"/>
       <x:c r="E44" s="5" t="s">
-        <x:v>562</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="F44" s="4"/>
       <x:c r="G44" s="4"/>
       <x:c r="H44" s="4"/>
       <x:c r="I44" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="J44" s="4"/>
       <x:c r="K44" s="4"/>
@@ -12477,22 +12478,22 @@
       <x:c r="R44" s="4"/>
       <x:c r="S44" s="4"/>
       <x:c r="T44" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="U44" s="4"/>
       <x:c r="V44" s="4"/>
       <x:c r="W44" s="5" t="s">
-        <x:v>558</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="X44" s="4"/>
       <x:c r="Y44" s="5" t="s">
-        <x:v>559</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="Z44" s="4"/>
       <x:c r="AA44" s="4"/>
       <x:c r="AB44" s="4"/>
       <x:c r="AC44" s="5" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="AD44" s="4"/>
       <x:c r="AE44" s="4"/>
@@ -12542,7 +12543,7 @@
       <x:c r="AF45" s="4"/>
       <x:c r="AG45" s="4"/>
       <x:c r="AH45" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AI45" s="4"/>
       <x:c r="AJ45" s="4"/>
@@ -12554,23 +12555,23 @@
     </x:row>
     <x:row r="46" spans="1:41">
       <x:c r="A46" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B46" s="4"/>
       <x:c r="C46" s="4"/>
       <x:c r="D46" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E46" s="4"/>
       <x:c r="F46" s="4"/>
       <x:c r="G46" s="4"/>
       <x:c r="H46" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I46" s="4"/>
       <x:c r="J46" s="4"/>
       <x:c r="K46" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="L46" s="4"/>
       <x:c r="M46" s="4"/>
@@ -12600,13 +12601,13 @@
       <x:c r="AK46" s="4"/>
       <x:c r="AL46" s="4"/>
       <x:c r="AM46" s="5" t="s">
-        <x:v>566</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="AN46" s="4"/>
       <x:c r="AO46" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1"/>
+  <x:sheetProtection password="8CAE" sheet="1" objects="1"/>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AO1"/>
     <x:mergeCell ref="A2:AO2"/>
@@ -12657,7 +12658,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:28" ht="24" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -12689,7 +12690,7 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="24" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="2"/>
       <x:c r="C2" s="2"/>
@@ -12722,7 +12723,7 @@
     <x:row r="3" spans="1:28">
       <x:c r="A3" s="4"/>
       <x:c r="B3" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
@@ -12730,7 +12731,7 @@
       <x:c r="F3" s="4"/>
       <x:c r="G3" s="4"/>
       <x:c r="H3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I3" s="4"/>
       <x:c r="J3" s="4"/>
@@ -12743,7 +12744,7 @@
       <x:c r="Q3" s="4"/>
       <x:c r="R3" s="4"/>
       <x:c r="S3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T3" s="4"/>
       <x:c r="U3" s="4"/>
@@ -12751,7 +12752,7 @@
       <x:c r="W3" s="4"/>
       <x:c r="X3" s="4"/>
       <x:c r="Y3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z3" s="4"/>
       <x:c r="AA3" s="4"/>
@@ -12760,7 +12761,7 @@
     <x:row r="4" spans="1:28">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C4" s="4"/>
       <x:c r="D4" s="4"/>
@@ -12772,7 +12773,7 @@
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M4" s="4"/>
       <x:c r="N4" s="4"/>
@@ -12781,7 +12782,7 @@
       <x:c r="Q4" s="4"/>
       <x:c r="R4" s="4"/>
       <x:c r="S4" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="T4" s="4"/>
       <x:c r="U4" s="4"/>
@@ -12790,7 +12791,7 @@
       <x:c r="X4" s="4"/>
       <x:c r="Y4" s="4"/>
       <x:c r="Z4" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AA4" s="4"/>
       <x:c r="AB4" s="4"/>
@@ -12798,7 +12799,7 @@
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="4"/>
       <x:c r="D5" s="4"/>
@@ -12810,7 +12811,7 @@
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
       <x:c r="L5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M5" s="4"/>
       <x:c r="N5" s="4"/>
@@ -12819,7 +12820,7 @@
       <x:c r="Q5" s="4"/>
       <x:c r="R5" s="4"/>
       <x:c r="S5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="T5" s="4"/>
       <x:c r="U5" s="4"/>
@@ -12827,7 +12828,7 @@
       <x:c r="W5" s="4"/>
       <x:c r="X5" s="4"/>
       <x:c r="Y5" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="Z5" s="4"/>
       <x:c r="AA5" s="4"/>
@@ -12836,7 +12837,7 @@
     <x:row r="6" spans="1:28">
       <x:c r="A6" s="4"/>
       <x:c r="B6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="4"/>
       <x:c r="D6" s="4"/>
@@ -12848,7 +12849,7 @@
       <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M6" s="4"/>
       <x:c r="N6" s="4"/>
@@ -12857,7 +12858,7 @@
       <x:c r="Q6" s="4"/>
       <x:c r="R6" s="4"/>
       <x:c r="S6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="T6" s="4"/>
       <x:c r="U6" s="4"/>
@@ -12867,14 +12868,14 @@
       <x:c r="Y6" s="4"/>
       <x:c r="Z6" s="4"/>
       <x:c r="AA6" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="AB6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:28">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -12883,7 +12884,7 @@
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
@@ -12895,7 +12896,7 @@
       <x:c r="Q7" s="4"/>
       <x:c r="R7" s="4"/>
       <x:c r="S7" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="T7" s="4"/>
       <x:c r="U7" s="4"/>
@@ -12905,21 +12906,21 @@
       <x:c r="Y7" s="4"/>
       <x:c r="Z7" s="4"/>
       <x:c r="AA7" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="AB7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:28">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4"/>
       <x:c r="D8" s="4"/>
       <x:c r="E8" s="4"/>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
@@ -12940,7 +12941,7 @@
       <x:c r="X8" s="4"/>
       <x:c r="Y8" s="4"/>
       <x:c r="Z8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AA8" s="4"/>
       <x:c r="AB8" s="4"/>
@@ -12955,7 +12956,7 @@
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="5" t="s">
-        <x:v>567</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -12972,7 +12973,7 @@
       <x:c r="V9" s="4"/>
       <x:c r="W9" s="4"/>
       <x:c r="X9" s="5" t="s">
-        <x:v>568</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="Y9" s="4"/>
       <x:c r="Z9" s="4"/>
@@ -12993,19 +12994,19 @@
       <x:c r="K10" s="4"/>
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="5" t="s">
-        <x:v>569</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="N10" s="4"/>
       <x:c r="O10" s="4"/>
       <x:c r="P10" s="5" t="s">
-        <x:v>570</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="Q10" s="4"/>
       <x:c r="R10" s="4"/>
       <x:c r="S10" s="4"/>
       <x:c r="T10" s="4"/>
       <x:c r="U10" s="5" t="s">
-        <x:v>571</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="V10" s="4"/>
       <x:c r="W10" s="4"/>
@@ -13022,7 +13023,7 @@
       <x:c r="D11" s="4"/>
       <x:c r="E11" s="4"/>
       <x:c r="F11" s="5" t="s">
-        <x:v>572</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="G11" s="4"/>
       <x:c r="H11" s="4"/>
@@ -13031,12 +13032,12 @@
       <x:c r="K11" s="4"/>
       <x:c r="L11" s="4"/>
       <x:c r="M11" s="5" t="s">
-        <x:v>573</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="N11" s="4"/>
       <x:c r="O11" s="4"/>
       <x:c r="P11" s="5" t="s">
-        <x:v>574</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="Q11" s="4"/>
       <x:c r="R11" s="4"/>
@@ -13069,7 +13070,7 @@
       <x:c r="O12" s="4"/>
       <x:c r="P12" s="4"/>
       <x:c r="Q12" s="5" t="s">
-        <x:v>575</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="R12" s="4"/>
       <x:c r="S12" s="4"/>
@@ -13086,7 +13087,7 @@
     <x:row r="13" spans="1:28">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="4"/>
       <x:c r="D13" s="4"/>
@@ -13100,13 +13101,13 @@
       <x:c r="L13" s="4"/>
       <x:c r="M13" s="4"/>
       <x:c r="N13" s="5" t="s">
-        <x:v>576</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="O13" s="4"/>
       <x:c r="P13" s="4"/>
       <x:c r="Q13" s="4"/>
       <x:c r="R13" s="5" t="s">
-        <x:v>577</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="S13" s="4"/>
       <x:c r="T13" s="4"/>
@@ -13124,7 +13125,7 @@
       <x:c r="B14" s="4"/>
       <x:c r="C14" s="4"/>
       <x:c r="D14" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="4"/>
       <x:c r="F14" s="4"/>
@@ -13154,7 +13155,7 @@
     <x:row r="15" spans="1:28">
       <x:c r="A15" s="4"/>
       <x:c r="B15" s="5" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -13168,13 +13169,13 @@
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
       <x:c r="N15" s="5" t="s">
-        <x:v>576</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="O15" s="4"/>
       <x:c r="P15" s="4"/>
       <x:c r="Q15" s="4"/>
       <x:c r="R15" s="5" t="s">
-        <x:v>577</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="S15" s="4"/>
       <x:c r="T15" s="4"/>
@@ -13190,7 +13191,7 @@
     <x:row r="16" spans="1:28">
       <x:c r="A16" s="4"/>
       <x:c r="B16" s="5" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C16" s="4"/>
       <x:c r="D16" s="4"/>
@@ -13204,7 +13205,7 @@
       <x:c r="L16" s="4"/>
       <x:c r="M16" s="4"/>
       <x:c r="N16" s="5" t="s">
-        <x:v>576</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="O16" s="4"/>
       <x:c r="P16" s="4"/>
@@ -13224,7 +13225,7 @@
     <x:row r="17" spans="1:28">
       <x:c r="A17" s="4"/>
       <x:c r="B17" s="5" t="s">
-        <x:v>578</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C17" s="4"/>
       <x:c r="D17" s="4"/>
@@ -13238,7 +13239,7 @@
       <x:c r="L17" s="4"/>
       <x:c r="M17" s="4"/>
       <x:c r="N17" s="6" t="s">
-        <x:v>512</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="O17" s="4"/>
       <x:c r="P17" s="4"/>
@@ -13259,7 +13260,7 @@
       <x:c r="A18" s="4"/>
       <x:c r="B18" s="4"/>
       <x:c r="C18" s="5" t="s">
-        <x:v>579</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D18" s="4"/>
       <x:c r="E18" s="4"/>
@@ -13293,7 +13294,7 @@
       <x:c r="C19" s="4"/>
       <x:c r="D19" s="4"/>
       <x:c r="E19" s="5" t="s">
-        <x:v>580</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F19" s="4"/>
       <x:c r="G19" s="4"/>
@@ -13323,7 +13324,7 @@
       <x:c r="A20" s="4"/>
       <x:c r="B20" s="4"/>
       <x:c r="C20" s="5" t="s">
-        <x:v>581</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D20" s="4"/>
       <x:c r="E20" s="4"/>
@@ -13333,7 +13334,7 @@
       <x:c r="I20" s="4"/>
       <x:c r="J20" s="4"/>
       <x:c r="K20" s="5" t="s">
-        <x:v>582</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="L20" s="4"/>
       <x:c r="M20" s="4"/>
@@ -13376,7 +13377,7 @@
       <x:c r="T21" s="4"/>
       <x:c r="U21" s="4"/>
       <x:c r="V21" s="5" t="s">
-        <x:v>583</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="W21" s="4"/>
       <x:c r="X21" s="4"/>
@@ -13406,7 +13407,7 @@
       <x:c r="R22" s="4"/>
       <x:c r="S22" s="4"/>
       <x:c r="T22" s="5" t="s">
-        <x:v>584</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="U22" s="4"/>
       <x:c r="V22" s="4"/>
@@ -13441,7 +13442,7 @@
       <x:c r="U23" s="4"/>
       <x:c r="V23" s="4"/>
       <x:c r="W23" s="5" t="s">
-        <x:v>585</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="X23" s="4"/>
       <x:c r="Y23" s="4"/>
@@ -13453,7 +13454,7 @@
       <x:c r="A24" s="4"/>
       <x:c r="B24" s="4"/>
       <x:c r="C24" s="5" t="s">
-        <x:v>586</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="D24" s="4"/>
       <x:c r="E24" s="4"/>
@@ -13486,7 +13487,7 @@
       <x:c r="B25" s="4"/>
       <x:c r="C25" s="4"/>
       <x:c r="D25" s="5" t="s">
-        <x:v>587</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="E25" s="4"/>
       <x:c r="F25" s="4"/>
@@ -13517,7 +13518,7 @@
       <x:c r="A26" s="4"/>
       <x:c r="B26" s="4"/>
       <x:c r="C26" s="5" t="s">
-        <x:v>581</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="D26" s="4"/>
       <x:c r="E26" s="4"/>
@@ -13526,7 +13527,7 @@
       <x:c r="H26" s="4"/>
       <x:c r="I26" s="4"/>
       <x:c r="J26" s="5" t="s">
-        <x:v>588</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="K26" s="4"/>
       <x:c r="L26" s="4"/>
@@ -13549,23 +13550,23 @@
     </x:row>
     <x:row r="27" spans="1:28">
       <x:c r="A27" s="5" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B27" s="4"/>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
       <x:c r="E27" s="5" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F27" s="4"/>
       <x:c r="G27" s="4"/>
       <x:c r="H27" s="5" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="I27" s="4"/>
       <x:c r="J27" s="4"/>
       <x:c r="K27" s="5" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="L27" s="4"/>
       <x:c r="M27" s="4"/>
@@ -13584,11 +13585,11 @@
       <x:c r="Z27" s="4"/>
       <x:c r="AA27" s="4"/>
       <x:c r="AB27" s="5" t="s">
-        <x:v>589</x:v>
+        <x:v>590</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:sheetProtection sheet="1" objects="1"/>
+  <x:sheetProtection password="8CAE" sheet="1" objects="1"/>
   <x:mergeCells count="2">
     <x:mergeCell ref="A1:AB1"/>
     <x:mergeCell ref="A2:AB2"/>
